--- a/gk-league-comparison/data/SWE2_2026.xlsx
+++ b/gk-league-comparison/data/SWE2_2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr date1904="false"/>
   <sheets>
-    <sheet name="Search results (18)" sheetId="1" r:id="rId4"/>
+    <sheet name="Search results (23)" sheetId="1" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -67,7 +67,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:DY19"/>
+  <dimension ref="A1:DY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="15.18988764044944"/>
@@ -82,11 +82,11 @@
     <col min="10" max="10" bestFit="true" customWidth="true" width="5.289887640449439"/>
     <col min="11" max="11" bestFit="true" customWidth="true" width="6.389887640449439"/>
     <col min="12" max="12" bestFit="true" customWidth="true" width="4.189887640449439"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="5.289887640449439"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="6.389887640449439"/>
     <col min="14" max="14" bestFit="true" customWidth="true" width="12.989887640449439"/>
     <col min="15" max="15" bestFit="true" customWidth="true" width="14.08988764044944"/>
     <col min="16" max="16" bestFit="true" customWidth="true" width="10.78988764044944"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="16.28988764044944"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="27.28988764044944"/>
     <col min="18" max="18" bestFit="true" customWidth="true" width="9.68988764044944"/>
     <col min="19" max="19" bestFit="true" customWidth="true" width="7.489887640449439"/>
     <col min="20" max="20" bestFit="true" customWidth="true" width="7.489887640449439"/>
@@ -851,17 +851,17 @@
     <row ht="12" customHeight="true" r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>H. Keto</t>
+          <t>A. Andersson</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr">
@@ -870,21 +870,21 @@
         </is>
       </c>
       <c r="E2" s="0" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H2" s="0" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>1286</v>
+        <v>1330</v>
       </c>
       <c r="J2" s="0" t="n">
         <v>0</v>
@@ -899,31 +899,31 @@
         <v>0.0</v>
       </c>
       <c r="N2" s="0" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="O2" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="P2" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q2" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="R2" s="0" t="inlineStr">
         <is>
-          <t>right</t>
+          <t/>
         </is>
       </c>
       <c r="S2" s="0" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="T2" s="0" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="U2" s="0" t="inlineStr">
         <is>
@@ -931,20 +931,20 @@
         </is>
       </c>
       <c r="V2" s="0" t="n">
-        <v>0.56</v>
+        <v>0.27</v>
       </c>
       <c r="W2" s="0" t="n">
-        <v>0.28</v>
+        <v>0.0</v>
       </c>
       <c r="X2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y2" s="0" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="Z2" s="0" t="n">
         <v>100.0</v>
       </c>
-      <c r="Y2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z2" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AA2" s="0" t="n">
         <v>0.0</v>
       </c>
@@ -955,10 +955,10 @@
         <v>0.0</v>
       </c>
       <c r="AD2" s="0" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="AE2" s="0" t="n">
-        <v>0.44</v>
+        <v>0.36</v>
       </c>
       <c r="AF2" s="0" t="n">
         <v>0.0</v>
@@ -976,7 +976,7 @@
         <v>0.0</v>
       </c>
       <c r="AK2" s="0" t="n">
-        <v>0.0</v>
+        <v>0.07</v>
       </c>
       <c r="AL2" s="0" t="n">
         <v>0.0</v>
@@ -1033,13 +1033,13 @@
         <v>0.0</v>
       </c>
       <c r="BD2" s="0" t="n">
-        <v>0.0</v>
+        <v>0.07</v>
       </c>
       <c r="BE2" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="BF2" s="0" t="n">
-        <v>0.07</v>
+        <v>0.2</v>
       </c>
       <c r="BG2" s="0" t="n">
         <v>100.0</v>
@@ -1054,146 +1054,146 @@
         <v>0.0</v>
       </c>
       <c r="BK2" s="0" t="n">
-        <v>13.09</v>
+        <v>18.47</v>
       </c>
       <c r="BL2" s="0" t="n">
-        <v>0.63</v>
+        <v>0.34</v>
       </c>
       <c r="BM2" s="0" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BN2" s="0" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="BO2" s="0" t="n">
+        <v>79.81</v>
+      </c>
+      <c r="BP2" s="0" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="BQ2" s="0" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="BR2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT2" s="0" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="BU2" s="0" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="BV2" s="0" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="BW2" s="0" t="n">
+        <v>98.07</v>
+      </c>
+      <c r="BX2" s="0" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="BY2" s="0" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="BZ2" s="0" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="CA2" s="0" t="n">
+        <v>51.01</v>
+      </c>
+      <c r="CB2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI2" s="0" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="CJ2" s="0" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="CK2" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CL2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CM2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CN2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CO2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CP2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CQ2" s="0" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="CR2" s="0" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="CS2" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT2" s="0" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CU2" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="CV2" s="0" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="CW2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX2" s="0" t="n">
+        <v>64.29</v>
+      </c>
+      <c r="CY2" s="0" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="CZ2" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DA2" s="0" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="DB2" s="0" t="n">
+        <v>-0.151</v>
+      </c>
+      <c r="DC2" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD2" s="0" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DE2" s="0" t="n">
         <v>0.07</v>
       </c>
-      <c r="BN2" s="0" t="n">
-        <v>25.19</v>
-      </c>
-      <c r="BO2" s="0" t="n">
-        <v>82.22</v>
-      </c>
-      <c r="BP2" s="0" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="BQ2" s="0" t="n">
-        <v>73.21</v>
-      </c>
-      <c r="BR2" s="0" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="BS2" s="0" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="BT2" s="0" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="BU2" s="0" t="n">
-        <v>94.93</v>
-      </c>
-      <c r="BV2" s="0" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="BW2" s="0" t="n">
-        <v>97.29</v>
-      </c>
-      <c r="BX2" s="0" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="BY2" s="0" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="BZ2" s="0" t="n">
-        <v>31.18</v>
-      </c>
-      <c r="CA2" s="0" t="n">
-        <v>49.41</v>
-      </c>
-      <c r="CB2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CC2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CD2" s="0" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="CE2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CF2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CG2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CH2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CI2" s="0" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CJ2" s="0" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="CK2" s="0" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="CL2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CM2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CN2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CO2" s="0" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="CP2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CQ2" s="0" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="CR2" s="0" t="n">
-        <v>68.38</v>
-      </c>
-      <c r="CS2" s="0" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT2" s="0" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CU2" s="0" t="n">
-        <v>62</v>
-      </c>
-      <c r="CV2" s="0" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="CW2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="CX2" s="0" t="n">
-        <v>59.68</v>
-      </c>
-      <c r="CY2" s="0" t="n">
-        <v>19.74</v>
-      </c>
-      <c r="CZ2" s="0" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DA2" s="0" t="n">
-        <v>-5.26</v>
-      </c>
-      <c r="DB2" s="0" t="n">
-        <v>-0.368</v>
-      </c>
-      <c r="DC2" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DD2" s="0" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="DE2" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="DF2" s="0" t="inlineStr">
         <is>
           <t/>
@@ -1219,62 +1219,62 @@
         <v>0.0</v>
       </c>
       <c r="DL2" s="0" t="n">
-        <v>5464.48</v>
+        <v>10969.78</v>
       </c>
       <c r="DM2" s="0" t="n">
-        <v>130.39</v>
+        <v>1721.24</v>
       </c>
       <c r="DN2" s="0" t="n">
-        <v>30.49</v>
+        <v>582.28</v>
       </c>
       <c r="DO2" s="0" t="n">
-        <v>3.04</v>
+        <v>222.34</v>
       </c>
       <c r="DP2" s="0" t="n">
-        <v>33.53</v>
+        <v>804.61</v>
       </c>
       <c r="DQ2" s="0" t="n">
-        <v>60.72</v>
+        <v>121.89</v>
       </c>
       <c r="DR2" s="0" t="n">
-        <v>32.59</v>
+        <v>33.26</v>
       </c>
       <c r="DS2" s="0" t="n">
-        <v>56.5</v>
+        <v>210.7</v>
       </c>
       <c r="DT2" s="0" t="n">
-        <v>4.69</v>
+        <v>30.82</v>
       </c>
       <c r="DU2" s="0" t="n">
-        <v>62.53</v>
+        <v>174.32</v>
       </c>
       <c r="DV2" s="0" t="n">
-        <v>4.69</v>
+        <v>35.88</v>
       </c>
       <c r="DW2" s="0" t="n">
-        <v>4.02</v>
+        <v>46.99</v>
       </c>
       <c r="DX2" s="0" t="n">
-        <v>0.45</v>
+        <v>15.16</v>
       </c>
       <c r="DY2" s="0" t="n">
-        <v>4.47</v>
+        <v>62.15</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>Amr Kaddoura</t>
+          <t>T. Krantz</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>IFK Norrköping</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>IFK Norrköping</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E3" s="0" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2028-12-31</t>
         </is>
       </c>
       <c r="H3" s="0" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>994</v>
+        <v>2191</v>
       </c>
       <c r="J3" s="0" t="n">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         <v>0.0</v>
       </c>
       <c r="N3" s="0" t="n">
-        <v>0.63</v>
+        <v>0.21</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>85.71</v>
+        <v>100.0</v>
       </c>
       <c r="P3" s="0" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="Q3" s="0" t="inlineStr">
         <is>
-          <t>Sweden, Palestine</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="R3" s="0" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="S3" s="0" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="T3" s="0" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="U3" s="0" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         </is>
       </c>
       <c r="V3" s="0" t="n">
-        <v>0.54</v>
+        <v>0.94</v>
       </c>
       <c r="W3" s="0" t="n">
-        <v>0.18</v>
+        <v>0.0</v>
       </c>
       <c r="X3" s="0" t="n">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y3" s="0" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="Z3" s="0" t="n">
         <v>100.0</v>
@@ -1368,19 +1368,19 @@
         <v>0.0</v>
       </c>
       <c r="AD3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.94</v>
       </c>
       <c r="AE3" s="0" t="n">
-        <v>0.65</v>
+        <v>1.35</v>
       </c>
       <c r="AF3" s="0" t="n">
-        <v>0.09</v>
+        <v>0.0</v>
       </c>
       <c r="AG3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="AH3" s="0" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="AI3" s="0" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0.0</v>
       </c>
       <c r="BF3" s="0" t="n">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
       <c r="BG3" s="0" t="n">
         <v>100.0</v>
@@ -1467,55 +1467,55 @@
         <v>0.0</v>
       </c>
       <c r="BK3" s="0" t="n">
-        <v>18.47</v>
+        <v>23.78</v>
       </c>
       <c r="BL3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
       <c r="BN3" s="0" t="n">
-        <v>31.96</v>
+        <v>38.37</v>
       </c>
       <c r="BO3" s="0" t="n">
-        <v>79.89</v>
+        <v>81.26</v>
       </c>
       <c r="BP3" s="0" t="n">
-        <v>16.21</v>
+        <v>19.27</v>
       </c>
       <c r="BQ3" s="0" t="n">
-        <v>66.48</v>
+        <v>69.08</v>
       </c>
       <c r="BR3" s="0" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="BS3" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="BT3" s="0" t="n">
-        <v>15.12</v>
+        <v>17.29</v>
       </c>
       <c r="BU3" s="0" t="n">
-        <v>93.41</v>
+        <v>93.59</v>
       </c>
       <c r="BV3" s="0" t="n">
-        <v>20.46</v>
+        <v>25.92</v>
       </c>
       <c r="BW3" s="0" t="n">
-        <v>96.9</v>
+        <v>95.4</v>
       </c>
       <c r="BX3" s="0" t="n">
-        <v>11.5</v>
+        <v>12.41</v>
       </c>
       <c r="BY3" s="0" t="n">
-        <v>49.61</v>
+        <v>51.99</v>
       </c>
       <c r="BZ3" s="0" t="n">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
       <c r="CA3" s="0" t="n">
-        <v>49.65</v>
+        <v>47.8</v>
       </c>
       <c r="CB3" s="0" t="n">
         <v>0.0</v>
@@ -1524,7 +1524,7 @@
         <v>0.0</v>
       </c>
       <c r="CD3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.08</v>
       </c>
       <c r="CE3" s="0" t="n">
         <v>0.0</v>
@@ -1539,22 +1539,22 @@
         <v>0.0</v>
       </c>
       <c r="CI3" s="0" t="n">
-        <v>3.71</v>
+        <v>3.82</v>
       </c>
       <c r="CJ3" s="0" t="n">
-        <v>34.15</v>
+        <v>38.71</v>
       </c>
       <c r="CK3" s="0" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="CL3" s="0" t="n">
-        <v>0.0</v>
+        <v>12.5</v>
       </c>
       <c r="CM3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="CN3" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="CO3" s="0" t="n">
         <v>0.0</v>
@@ -1563,131 +1563,131 @@
         <v>0.0</v>
       </c>
       <c r="CQ3" s="0" t="n">
-        <v>7.33</v>
+        <v>9.24</v>
       </c>
       <c r="CR3" s="0" t="n">
-        <v>59.26</v>
+        <v>60.44</v>
       </c>
       <c r="CS3" s="0" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CT3" s="0" t="n">
-        <v>0.81</v>
+        <v>0.58</v>
       </c>
       <c r="CU3" s="0" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="CV3" s="0" t="n">
-        <v>2.99</v>
+        <v>3.66</v>
       </c>
       <c r="CW3" s="0" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="CX3" s="0" t="n">
-        <v>72.73</v>
+        <v>84.27</v>
       </c>
       <c r="CY3" s="0" t="n">
-        <v>10.04</v>
+        <v>21.88</v>
       </c>
       <c r="CZ3" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DA3" s="0" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="DB3" s="0" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="DC3" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD3" s="0" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DE3" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="DF3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DG3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DH3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DI3" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DJ3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK3" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DL3" s="0" t="n">
+        <v>6675.72</v>
+      </c>
+      <c r="DM3" s="0" t="n">
+        <v>252.13</v>
+      </c>
+      <c r="DN3" s="0" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="DO3" s="0" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="DP3" s="0" t="n">
+        <v>121.78</v>
+      </c>
+      <c r="DQ3" s="0" t="n">
+        <v>74.17</v>
+      </c>
+      <c r="DR3" s="0" t="n">
+        <v>32.34</v>
+      </c>
+      <c r="DS3" s="0" t="n">
+        <v>87.45</v>
+      </c>
+      <c r="DT3" s="0" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="DU3" s="0" t="n">
+        <v>85.19</v>
+      </c>
+      <c r="DV3" s="0" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="DW3" s="0" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="DX3" s="0" t="n">
         <v>0.91</v>
       </c>
-      <c r="DA3" s="0" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="DB3" s="0" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="DC3" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DD3" s="0" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DE3" s="0" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DF3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DG3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DH3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DI3" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DJ3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK3" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DL3" s="0" t="n">
-        <v>6190.44</v>
-      </c>
-      <c r="DM3" s="0" t="n">
-        <v>231.73</v>
-      </c>
-      <c r="DN3" s="0" t="n">
-        <v>53.59</v>
-      </c>
-      <c r="DO3" s="0" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="DP3" s="0" t="n">
-        <v>65.42</v>
-      </c>
-      <c r="DQ3" s="0" t="n">
-        <v>68.78</v>
-      </c>
-      <c r="DR3" s="0" t="n">
-        <v>29.69</v>
-      </c>
-      <c r="DS3" s="0" t="n">
-        <v>86.77</v>
-      </c>
-      <c r="DT3" s="0" t="n">
-        <v>11.54</v>
-      </c>
-      <c r="DU3" s="0" t="n">
-        <v>90.0</v>
-      </c>
-      <c r="DV3" s="0" t="n">
-        <v>9.69</v>
-      </c>
-      <c r="DW3" s="0" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="DX3" s="0" t="n">
-        <v>0.92</v>
-      </c>
       <c r="DY3" s="0" t="n">
-        <v>7.38</v>
+        <v>12.69</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>V. Frodig</t>
+          <t>Amr Kaddoura</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E4" s="0" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="H4" s="0" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>1193</v>
+        <v>1674</v>
       </c>
       <c r="J4" s="0" t="n">
         <v>0</v>
@@ -1719,16 +1719,16 @@
         <v>0.0</v>
       </c>
       <c r="L4" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="N4" s="0" t="n">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>100.0</v>
+        <v>91.67</v>
       </c>
       <c r="P4" s="0" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="Q4" s="0" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Sweden, Palestine</t>
         </is>
       </c>
       <c r="R4" s="0" t="inlineStr">
@@ -1749,7 +1749,7 @@
         <v>185</v>
       </c>
       <c r="T4" s="0" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U4" s="0" t="inlineStr">
         <is>
@@ -1757,20 +1757,20 @@
         </is>
       </c>
       <c r="V4" s="0" t="n">
-        <v>1.06</v>
+        <v>0.59</v>
       </c>
       <c r="W4" s="0" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="X4" s="0" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="Y4" s="0" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Z4" s="0" t="n">
         <v>100.0</v>
       </c>
-      <c r="Y4" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z4" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AA4" s="0" t="n">
         <v>0.0</v>
       </c>
@@ -1781,19 +1781,19 @@
         <v>0.0</v>
       </c>
       <c r="AD4" s="0" t="n">
-        <v>0.98</v>
+        <v>0.54</v>
       </c>
       <c r="AE4" s="0" t="n">
-        <v>1.33</v>
+        <v>0.77</v>
       </c>
       <c r="AF4" s="0" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="AG4" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH4" s="0" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="AI4" s="0" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0.0</v>
       </c>
       <c r="AV4" s="0" t="n">
-        <v>0.08</v>
+        <v>0.0</v>
       </c>
       <c r="AW4" s="0" t="n">
         <v>0.0</v>
@@ -1865,7 +1865,7 @@
         <v>0.0</v>
       </c>
       <c r="BF4" s="0" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="BG4" s="0" t="n">
         <v>100.0</v>
@@ -1880,55 +1880,55 @@
         <v>0.0</v>
       </c>
       <c r="BK4" s="0" t="n">
-        <v>9.73</v>
+        <v>22.15</v>
       </c>
       <c r="BL4" s="0" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BM4" s="0" t="n">
-        <v>0.23</v>
+        <v>0.54</v>
       </c>
       <c r="BN4" s="0" t="n">
-        <v>19.24</v>
+        <v>35.11</v>
       </c>
       <c r="BO4" s="0" t="n">
-        <v>81.18</v>
+        <v>81.62</v>
       </c>
       <c r="BP4" s="0" t="n">
-        <v>10.86</v>
+        <v>17.26</v>
       </c>
       <c r="BQ4" s="0" t="n">
-        <v>70.14</v>
+        <v>67.29</v>
       </c>
       <c r="BR4" s="0" t="n">
-        <v>0.0</v>
+        <v>0.11</v>
       </c>
       <c r="BS4" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="BT4" s="0" t="n">
-        <v>7.09</v>
+        <v>16.94</v>
       </c>
       <c r="BU4" s="0" t="n">
-        <v>94.68</v>
+        <v>95.56</v>
       </c>
       <c r="BV4" s="0" t="n">
-        <v>12.6</v>
+        <v>23.12</v>
       </c>
       <c r="BW4" s="0" t="n">
-        <v>97.6</v>
+        <v>97.91</v>
       </c>
       <c r="BX4" s="0" t="n">
-        <v>6.64</v>
+        <v>11.99</v>
       </c>
       <c r="BY4" s="0" t="n">
-        <v>50.0</v>
+        <v>50.22</v>
       </c>
       <c r="BZ4" s="0" t="n">
-        <v>32.11</v>
+        <v>30.93</v>
       </c>
       <c r="CA4" s="0" t="n">
-        <v>52.04</v>
+        <v>49.33</v>
       </c>
       <c r="CB4" s="0" t="n">
         <v>0.0</v>
@@ -1949,16 +1949,16 @@
         <v>0.0</v>
       </c>
       <c r="CH4" s="0" t="n">
-        <v>0.08</v>
+        <v>0.0</v>
       </c>
       <c r="CI4" s="0" t="n">
-        <v>2.49</v>
+        <v>3.82</v>
       </c>
       <c r="CJ4" s="0" t="n">
-        <v>27.27</v>
+        <v>38.03</v>
       </c>
       <c r="CK4" s="0" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="CL4" s="0" t="n">
         <v>0.0</v>
@@ -1976,49 +1976,49 @@
         <v>0.0</v>
       </c>
       <c r="CQ4" s="0" t="n">
-        <v>4.98</v>
+        <v>8.06</v>
       </c>
       <c r="CR4" s="0" t="n">
-        <v>65.15</v>
+        <v>62.67</v>
       </c>
       <c r="CS4" s="0" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="CT4" s="0" t="n">
-        <v>1.58</v>
+        <v>0.91</v>
       </c>
       <c r="CU4" s="0" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="CV4" s="0" t="n">
-        <v>3.77</v>
+        <v>3.28</v>
       </c>
       <c r="CW4" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CX4" s="0" t="n">
-        <v>58.0</v>
+        <v>72.13</v>
       </c>
       <c r="CY4" s="0" t="n">
-        <v>17.9</v>
+        <v>17.46</v>
       </c>
       <c r="CZ4" s="0" t="n">
-        <v>1.35</v>
+        <v>0.94</v>
       </c>
       <c r="DA4" s="0" t="n">
-        <v>-3.1</v>
+        <v>0.46</v>
       </c>
       <c r="DB4" s="0" t="n">
-        <v>-0.234</v>
+        <v>0.025</v>
       </c>
       <c r="DC4" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD4" s="0" t="n">
-        <v>2.26</v>
+        <v>1.13</v>
       </c>
       <c r="DE4" s="0" t="n">
-        <v>0.0</v>
+        <v>0.22</v>
       </c>
       <c r="DF4" s="0" t="inlineStr">
         <is>
@@ -2045,62 +2045,62 @@
         <v>0.0</v>
       </c>
       <c r="DL4" s="0" t="n">
-        <v>5414.59</v>
+        <v>6190.44</v>
       </c>
       <c r="DM4" s="0" t="n">
-        <v>93.61</v>
+        <v>231.73</v>
       </c>
       <c r="DN4" s="0" t="n">
-        <v>19.78</v>
+        <v>53.59</v>
       </c>
       <c r="DO4" s="0" t="n">
-        <v>5.68</v>
+        <v>11.83</v>
       </c>
       <c r="DP4" s="0" t="n">
-        <v>25.47</v>
+        <v>65.42</v>
       </c>
       <c r="DQ4" s="0" t="n">
-        <v>60.16</v>
+        <v>68.78</v>
       </c>
       <c r="DR4" s="0" t="n">
-        <v>26.49</v>
+        <v>29.69</v>
       </c>
       <c r="DS4" s="0" t="n">
-        <v>58.25</v>
+        <v>86.77</v>
       </c>
       <c r="DT4" s="0" t="n">
-        <v>3.16</v>
+        <v>11.54</v>
       </c>
       <c r="DU4" s="0" t="n">
-        <v>62.31</v>
+        <v>90.0</v>
       </c>
       <c r="DV4" s="0" t="n">
-        <v>3.16</v>
+        <v>9.69</v>
       </c>
       <c r="DW4" s="0" t="n">
-        <v>3.16</v>
+        <v>6.46</v>
       </c>
       <c r="DX4" s="0" t="n">
-        <v>0.45</v>
+        <v>0.92</v>
       </c>
       <c r="DY4" s="0" t="n">
-        <v>3.61</v>
+        <v>7.38</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>J. Brattberg</t>
+          <t>S. Banozic</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -2109,27 +2109,27 @@
         </is>
       </c>
       <c r="E5" s="0" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H5" s="0" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>1394</v>
+        <v>2421</v>
       </c>
       <c r="J5" s="0" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.08</v>
+        <v>0.0</v>
       </c>
       <c r="L5" s="0" t="n">
         <v>0</v>
@@ -2138,10 +2138,10 @@
         <v>0.0</v>
       </c>
       <c r="N5" s="0" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
@@ -2155,14 +2155,14 @@
       </c>
       <c r="R5" s="0" t="inlineStr">
         <is>
-          <t>right</t>
+          <t/>
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="T5" s="0" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="U5" s="0" t="inlineStr">
         <is>
@@ -2170,268 +2170,268 @@
         </is>
       </c>
       <c r="V5" s="0" t="n">
-        <v>1.1</v>
+        <v>0.74</v>
       </c>
       <c r="W5" s="0" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="X5" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="Y5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD5" s="0" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AE5" s="0" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AF5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK5" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AL5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AT5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF5" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG5" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BH5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BJ5" s="0" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="BK5" s="0" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="BL5" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BM5" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BN5" s="0" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="BO5" s="0" t="n">
+        <v>82.99</v>
+      </c>
+      <c r="BP5" s="0" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="BQ5" s="0" t="n">
+        <v>71.82</v>
+      </c>
+      <c r="BR5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT5" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="BU5" s="0" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="BV5" s="0" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="BW5" s="0" t="n">
+        <v>97.91</v>
+      </c>
+      <c r="BX5" s="0" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="BY5" s="0" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="BZ5" s="0" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="CA5" s="0" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="CB5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE5" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CF5" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CG5" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="CH5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI5" s="0" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="CJ5" s="0" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="CK5" s="0" t="n">
         <v>0.26</v>
       </c>
-      <c r="Z5" s="0" t="n">
+      <c r="CL5" s="0" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="CM5" s="0" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="CN5" s="0" t="n">
         <v>100.0</v>
       </c>
-      <c r="AA5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD5" s="0" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AE5" s="0" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="0" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK5" s="0" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AL5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AO5" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AP5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AR5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" s="0" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AT5" s="0" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AU5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AV5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AW5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AX5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AY5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AZ5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BA5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BB5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BC5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BD5" s="0" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BE5" s="0" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BF5" s="0" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BG5" s="0" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="BH5" s="0" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BI5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BK5" s="0" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="BL5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BM5" s="0" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BN5" s="0" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="BO5" s="0" t="n">
-        <v>83.45</v>
-      </c>
-      <c r="BP5" s="0" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="BQ5" s="0" t="n">
-        <v>71.15</v>
-      </c>
-      <c r="BR5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT5" s="0" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="BU5" s="0" t="n">
-        <v>94.51</v>
-      </c>
-      <c r="BV5" s="0" t="n">
-        <v>20.08</v>
-      </c>
-      <c r="BW5" s="0" t="n">
-        <v>98.39</v>
-      </c>
-      <c r="BX5" s="0" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="BY5" s="0" t="n">
-        <v>44.07</v>
-      </c>
-      <c r="BZ5" s="0" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="CA5" s="0" t="n">
-        <v>51.82</v>
-      </c>
-      <c r="CB5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CC5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CD5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CE5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CF5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CG5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CH5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CI5" s="0" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CJ5" s="0" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="CK5" s="0" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="CL5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CM5" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CN5" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="CO5" s="0" t="n">
-        <v>0.0</v>
+        <v>0.07</v>
       </c>
       <c r="CP5" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ5" s="0" t="n">
-        <v>5.68</v>
+        <v>8.96</v>
       </c>
       <c r="CR5" s="0" t="n">
-        <v>60.23</v>
+        <v>67.63</v>
       </c>
       <c r="CS5" s="0" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="CT5" s="0" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="CU5" s="0" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="CV5" s="0" t="n">
-        <v>5.49</v>
+        <v>4.09</v>
       </c>
       <c r="CW5" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CX5" s="0" t="n">
-        <v>65.88</v>
+        <v>68.18</v>
       </c>
       <c r="CY5" s="0" t="n">
-        <v>27.13</v>
+        <v>37.09</v>
       </c>
       <c r="CZ5" s="0" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="DA5" s="0" t="n">
-        <v>-1.87</v>
+        <v>2.09</v>
       </c>
       <c r="DB5" s="0" t="n">
-        <v>-0.121</v>
+        <v>0.078</v>
       </c>
       <c r="DC5" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD5" s="0" t="n">
-        <v>2.0</v>
+        <v>1.71</v>
       </c>
       <c r="DE5" s="0" t="n">
-        <v>0.26</v>
+        <v>0.0</v>
       </c>
       <c r="DF5" s="0" t="inlineStr">
         <is>
@@ -2458,62 +2458,62 @@
         <v>0.0</v>
       </c>
       <c r="DL5" s="0" t="n">
-        <v>5698.63</v>
+        <v>6110.42</v>
       </c>
       <c r="DM5" s="0" t="n">
-        <v>86.29</v>
+        <v>183.89</v>
       </c>
       <c r="DN5" s="0" t="n">
-        <v>11.27</v>
+        <v>48.98</v>
       </c>
       <c r="DO5" s="0" t="n">
-        <v>0.32</v>
+        <v>21.62</v>
       </c>
       <c r="DP5" s="0" t="n">
-        <v>11.58</v>
+        <v>70.6</v>
       </c>
       <c r="DQ5" s="0" t="n">
-        <v>63.32</v>
+        <v>67.89</v>
       </c>
       <c r="DR5" s="0" t="n">
-        <v>25.15</v>
+        <v>34.16</v>
       </c>
       <c r="DS5" s="0" t="n">
-        <v>60.36</v>
+        <v>69.69</v>
       </c>
       <c r="DT5" s="0" t="n">
-        <v>2.75</v>
+        <v>6.35</v>
       </c>
       <c r="DU5" s="0" t="n">
-        <v>56.0</v>
+        <v>77.89</v>
       </c>
       <c r="DV5" s="0" t="n">
-        <v>4.13</v>
+        <v>7.14</v>
       </c>
       <c r="DW5" s="0" t="n">
-        <v>1.38</v>
+        <v>4.36</v>
       </c>
       <c r="DX5" s="0" t="n">
-        <v>0.0</v>
+        <v>1.85</v>
       </c>
       <c r="DY5" s="0" t="n">
-        <v>1.38</v>
+        <v>6.22</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>J. Olsson</t>
+          <t>M. Sætra</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -2522,21 +2522,21 @@
         </is>
       </c>
       <c r="E6" s="0" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>225000</v>
+        <v>150000</v>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>2028-12-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H6" s="0" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>1378</v>
+        <v>2318</v>
       </c>
       <c r="J6" s="0" t="n">
         <v>0</v>
@@ -2548,22 +2548,22 @@
         <v>0</v>
       </c>
       <c r="M6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.25</v>
       </c>
       <c r="N6" s="0" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>100.0</v>
+        <v>92.31</v>
       </c>
       <c r="P6" s="0" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="Q6" s="0" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="R6" s="0" t="inlineStr">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="S6" s="0" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="T6" s="0" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="U6" s="0" t="inlineStr">
         <is>
@@ -2583,16 +2583,16 @@
         </is>
       </c>
       <c r="V6" s="0" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="W6" s="0" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="X6" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="Y6" s="0" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="Z6" s="0" t="n">
         <v>100.0</v>
@@ -2607,19 +2607,19 @@
         <v>0.0</v>
       </c>
       <c r="AD6" s="0" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AE6" s="0" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="AF6" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="AG6" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AI6" s="0" t="n">
         <v>0</v>
@@ -2628,7 +2628,7 @@
         <v>0.0</v>
       </c>
       <c r="AK6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.08</v>
       </c>
       <c r="AL6" s="0" t="n">
         <v>0.0</v>
@@ -2685,13 +2685,13 @@
         <v>0.0</v>
       </c>
       <c r="BD6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.08</v>
       </c>
       <c r="BE6" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="BF6" s="0" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="BG6" s="0" t="n">
         <v>100.0</v>
@@ -2703,70 +2703,70 @@
         <v>0.0</v>
       </c>
       <c r="BJ6" s="0" t="n">
-        <v>0.2</v>
+        <v>0.0</v>
       </c>
       <c r="BK6" s="0" t="n">
-        <v>13.19</v>
+        <v>15.41</v>
       </c>
       <c r="BL6" s="0" t="n">
-        <v>0.59</v>
+        <v>0.16</v>
       </c>
       <c r="BM6" s="0" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="BN6" s="0" t="n">
-        <v>23.45</v>
+        <v>27.02</v>
       </c>
       <c r="BO6" s="0" t="n">
-        <v>78.83</v>
+        <v>76.29</v>
       </c>
       <c r="BP6" s="0" t="n">
-        <v>13.78</v>
+        <v>16.11</v>
       </c>
       <c r="BQ6" s="0" t="n">
-        <v>67.77</v>
+        <v>61.93</v>
       </c>
       <c r="BR6" s="0" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="BS6" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="BT6" s="0" t="n">
-        <v>8.16</v>
+        <v>9.71</v>
       </c>
       <c r="BU6" s="0" t="n">
-        <v>94.4</v>
+        <v>97.6</v>
       </c>
       <c r="BV6" s="0" t="n">
-        <v>14.17</v>
+        <v>14.37</v>
       </c>
       <c r="BW6" s="0" t="n">
-        <v>97.7</v>
+        <v>97.3</v>
       </c>
       <c r="BX6" s="0" t="n">
-        <v>9.21</v>
+        <v>12.58</v>
       </c>
       <c r="BY6" s="0" t="n">
-        <v>50.35</v>
+        <v>52.78</v>
       </c>
       <c r="BZ6" s="0" t="n">
-        <v>34.96</v>
+        <v>38.71</v>
       </c>
       <c r="CA6" s="0" t="n">
-        <v>53.35</v>
+        <v>55.54</v>
       </c>
       <c r="CB6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
       <c r="CC6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="CD6" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CE6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="CF6" s="0" t="n">
         <v>0.0</v>
@@ -2775,19 +2775,19 @@
         <v>0.0</v>
       </c>
       <c r="CH6" s="0" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="CI6" s="0" t="n">
-        <v>3.4</v>
+        <v>6.45</v>
       </c>
       <c r="CJ6" s="0" t="n">
-        <v>38.46</v>
+        <v>49.4</v>
       </c>
       <c r="CK6" s="0" t="n">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
       <c r="CL6" s="0" t="n">
-        <v>16.67</v>
+        <v>18.75</v>
       </c>
       <c r="CM6" s="0" t="n">
         <v>0.0</v>
@@ -2796,55 +2796,55 @@
         <v>0.0</v>
       </c>
       <c r="CO6" s="0" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="CP6" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ6" s="0" t="n">
-        <v>7.05</v>
+        <v>8.27</v>
       </c>
       <c r="CR6" s="0" t="n">
-        <v>66.67</v>
+        <v>77.46</v>
       </c>
       <c r="CS6" s="0" t="n">
         <v>31</v>
       </c>
       <c r="CT6" s="0" t="n">
-        <v>2.02</v>
+        <v>1.2</v>
       </c>
       <c r="CU6" s="0" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="CV6" s="0" t="n">
-        <v>5.09</v>
+        <v>3.57</v>
       </c>
       <c r="CW6" s="0" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="CX6" s="0" t="n">
-        <v>60.26</v>
+        <v>66.3</v>
       </c>
       <c r="CY6" s="0" t="n">
-        <v>23.18</v>
+        <v>25.59</v>
       </c>
       <c r="CZ6" s="0" t="n">
-        <v>1.51</v>
+        <v>0.99</v>
       </c>
       <c r="DA6" s="0" t="n">
-        <v>-7.82</v>
+        <v>-5.41</v>
       </c>
       <c r="DB6" s="0" t="n">
-        <v>-0.511</v>
+        <v>-0.21</v>
       </c>
       <c r="DC6" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD6" s="0" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="DE6" s="0" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="DF6" s="0" t="inlineStr">
         <is>
@@ -2871,62 +2871,62 @@
         <v>0.0</v>
       </c>
       <c r="DL6" s="0" t="n">
-        <v>5696.36</v>
+        <v>5808.29</v>
       </c>
       <c r="DM6" s="0" t="n">
-        <v>161.32</v>
+        <v>150.89</v>
       </c>
       <c r="DN6" s="0" t="n">
-        <v>45.56</v>
+        <v>27.14</v>
       </c>
       <c r="DO6" s="0" t="n">
-        <v>9.57</v>
+        <v>3.58</v>
       </c>
       <c r="DP6" s="0" t="n">
-        <v>55.13</v>
+        <v>30.72</v>
       </c>
       <c r="DQ6" s="0" t="n">
-        <v>63.29</v>
+        <v>64.54</v>
       </c>
       <c r="DR6" s="0" t="n">
-        <v>29.11</v>
+        <v>31.87</v>
       </c>
       <c r="DS6" s="0" t="n">
-        <v>63.54</v>
+        <v>70.97</v>
       </c>
       <c r="DT6" s="0" t="n">
-        <v>8.33</v>
+        <v>3.12</v>
       </c>
       <c r="DU6" s="0" t="n">
-        <v>65.7</v>
+        <v>66.6</v>
       </c>
       <c r="DV6" s="0" t="n">
-        <v>7.71</v>
+        <v>4.84</v>
       </c>
       <c r="DW6" s="0" t="n">
-        <v>4.01</v>
+        <v>3.12</v>
       </c>
       <c r="DX6" s="0" t="n">
-        <v>0.93</v>
+        <v>0.47</v>
       </c>
       <c r="DY6" s="0" t="n">
-        <v>4.93</v>
+        <v>3.59</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>W. Eskelinen</t>
+          <t>O. Lindell</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E7" s="0" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>225000</v>
+        <v>150000</v>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-12-29</t>
         </is>
       </c>
       <c r="H7" s="0" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>1355</v>
+        <v>1673</v>
       </c>
       <c r="J7" s="0" t="n">
         <v>0</v>
@@ -2964,10 +2964,10 @@
         <v>0.0</v>
       </c>
       <c r="N7" s="0" t="n">
-        <v>0.07</v>
+        <v>0.65</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>100.0</v>
+        <v>75.0</v>
       </c>
       <c r="P7" s="0" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="S7" s="0" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="T7" s="0" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="U7" s="0" t="inlineStr">
         <is>
@@ -2996,19 +2996,19 @@
         </is>
       </c>
       <c r="V7" s="0" t="n">
-        <v>0.53</v>
+        <v>1.02</v>
       </c>
       <c r="W7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.11</v>
       </c>
       <c r="X7" s="0" t="n">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="Y7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.22</v>
       </c>
       <c r="Z7" s="0" t="n">
-        <v>0.0</v>
+        <v>75.0</v>
       </c>
       <c r="AA7" s="0" t="n">
         <v>0.0</v>
@@ -3020,19 +3020,19 @@
         <v>0.0</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.53</v>
+        <v>0.97</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.71</v>
+        <v>1.43</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="AG7" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.11</v>
       </c>
       <c r="AI7" s="0" t="n">
         <v>0</v>
@@ -3104,10 +3104,10 @@
         <v>0.0</v>
       </c>
       <c r="BF7" s="0" t="n">
-        <v>0.07</v>
+        <v>0.32</v>
       </c>
       <c r="BG7" s="0" t="n">
-        <v>100.0</v>
+        <v>83.33</v>
       </c>
       <c r="BH7" s="0" t="n">
         <v>0.0</v>
@@ -3116,58 +3116,58 @@
         <v>0.0</v>
       </c>
       <c r="BJ7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="BK7" s="0" t="n">
-        <v>12.22</v>
+        <v>21.36</v>
       </c>
       <c r="BL7" s="0" t="n">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="BM7" s="0" t="n">
-        <v>0.07</v>
+        <v>0.43</v>
       </c>
       <c r="BN7" s="0" t="n">
-        <v>20.72</v>
+        <v>36.63</v>
       </c>
       <c r="BO7" s="0" t="n">
-        <v>77.56</v>
+        <v>86.2</v>
       </c>
       <c r="BP7" s="0" t="n">
-        <v>12.15</v>
+        <v>17.54</v>
       </c>
       <c r="BQ7" s="0" t="n">
-        <v>65.57</v>
+        <v>76.07</v>
       </c>
       <c r="BR7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.11</v>
       </c>
       <c r="BS7" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BT7" s="0" t="n">
-        <v>7.77</v>
+        <v>17.48</v>
       </c>
       <c r="BU7" s="0" t="n">
-        <v>94.87</v>
+        <v>96.62</v>
       </c>
       <c r="BV7" s="0" t="n">
-        <v>11.76</v>
+        <v>27.11</v>
       </c>
       <c r="BW7" s="0" t="n">
-        <v>96.05</v>
+        <v>98.41</v>
       </c>
       <c r="BX7" s="0" t="n">
-        <v>8.97</v>
+        <v>9.31</v>
       </c>
       <c r="BY7" s="0" t="n">
-        <v>53.33</v>
+        <v>52.6</v>
       </c>
       <c r="BZ7" s="0" t="n">
-        <v>35.84</v>
+        <v>26.58</v>
       </c>
       <c r="CA7" s="0" t="n">
-        <v>51.32</v>
+        <v>47.29</v>
       </c>
       <c r="CB7" s="0" t="n">
         <v>0.0</v>
@@ -3191,16 +3191,16 @@
         <v>0.0</v>
       </c>
       <c r="CI7" s="0" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="CJ7" s="0" t="n">
-        <v>44.44</v>
+        <v>35.85</v>
       </c>
       <c r="CK7" s="0" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="CL7" s="0" t="n">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="CM7" s="0" t="n">
         <v>0.0</v>
@@ -3209,55 +3209,55 @@
         <v>0.0</v>
       </c>
       <c r="CO7" s="0" t="n">
-        <v>0.07</v>
+        <v>0.0</v>
       </c>
       <c r="CP7" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ7" s="0" t="n">
-        <v>7.24</v>
+        <v>6.89</v>
       </c>
       <c r="CR7" s="0" t="n">
-        <v>68.81</v>
+        <v>62.5</v>
       </c>
       <c r="CS7" s="0" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="CT7" s="0" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="CU7" s="0" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="CV7" s="0" t="n">
-        <v>3.79</v>
+        <v>4.14</v>
       </c>
       <c r="CW7" s="0" t="n">
         <v>4</v>
       </c>
       <c r="CX7" s="0" t="n">
-        <v>63.16</v>
+        <v>68.83</v>
       </c>
       <c r="CY7" s="0" t="n">
-        <v>15.9</v>
+        <v>24.41</v>
       </c>
       <c r="CZ7" s="0" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="DA7" s="0" t="n">
-        <v>-5.1</v>
+        <v>0.41</v>
       </c>
       <c r="DB7" s="0" t="n">
-        <v>-0.339</v>
+        <v>0.022</v>
       </c>
       <c r="DC7" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD7" s="0" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DE7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.22</v>
       </c>
       <c r="DF7" s="0" t="inlineStr">
         <is>
@@ -3284,62 +3284,62 @@
         <v>0.0</v>
       </c>
       <c r="DL7" s="0" t="n">
-        <v>5543.65</v>
+        <v>5777.23</v>
       </c>
       <c r="DM7" s="0" t="n">
-        <v>76.46</v>
+        <v>87.24</v>
       </c>
       <c r="DN7" s="0" t="n">
-        <v>17.27</v>
+        <v>26.98</v>
       </c>
       <c r="DO7" s="0" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="DP7" s="0" t="n">
-        <v>18.8</v>
+        <v>29.14</v>
       </c>
       <c r="DQ7" s="0" t="n">
-        <v>61.6</v>
+        <v>64.19</v>
       </c>
       <c r="DR7" s="0" t="n">
-        <v>29.04</v>
+        <v>26.8</v>
       </c>
       <c r="DS7" s="0" t="n">
-        <v>45.09</v>
+        <v>60.42</v>
       </c>
       <c r="DT7" s="0" t="n">
-        <v>5.04</v>
+        <v>6.73</v>
       </c>
       <c r="DU7" s="0" t="n">
-        <v>50.58</v>
+        <v>65.01</v>
       </c>
       <c r="DV7" s="0" t="n">
-        <v>6.18</v>
+        <v>6.58</v>
       </c>
       <c r="DW7" s="0" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="DX7" s="0" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="DY7" s="0" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>J. Ojrzyński</t>
+          <t>J. Brattberg</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -3348,27 +3348,27 @@
         </is>
       </c>
       <c r="E8" s="0" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="H8" s="0" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>1400</v>
+        <v>1879</v>
       </c>
       <c r="J8" s="0" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.08</v>
       </c>
       <c r="L8" s="0" t="n">
         <v>0</v>
@@ -3377,19 +3377,19 @@
         <v>0.0</v>
       </c>
       <c r="N8" s="0" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="O8" s="0" t="n">
         <v>84.62</v>
       </c>
       <c r="P8" s="0" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q8" s="0" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="R8" s="0" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="S8" s="0" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="T8" s="0" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="U8" s="0" t="inlineStr">
         <is>
@@ -3409,19 +3409,19 @@
         </is>
       </c>
       <c r="V8" s="0" t="n">
-        <v>0.51</v>
+        <v>1.1</v>
       </c>
       <c r="W8" s="0" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="X8" s="0" t="n">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="Y8" s="0" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="Z8" s="0" t="n">
-        <v>83.33</v>
+        <v>100.0</v>
       </c>
       <c r="AA8" s="0" t="n">
         <v>0.0</v>
@@ -3433,10 +3433,10 @@
         <v>0.0</v>
       </c>
       <c r="AD8" s="0" t="n">
-        <v>0.45</v>
+        <v>1.05</v>
       </c>
       <c r="AE8" s="0" t="n">
-        <v>0.56</v>
+        <v>1.43</v>
       </c>
       <c r="AF8" s="0" t="n">
         <v>0.0</v>
@@ -3445,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="AH8" s="0" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AI8" s="0" t="n">
         <v>0</v>
@@ -3454,7 +3454,7 @@
         <v>0.0</v>
       </c>
       <c r="AK8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.14</v>
       </c>
       <c r="AL8" s="0" t="n">
         <v>0.0</v>
@@ -3475,13 +3475,13 @@
         <v>0.0</v>
       </c>
       <c r="AR8" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="AT8" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="AU8" s="0" t="n">
         <v>0.0</v>
@@ -3511,19 +3511,19 @@
         <v>0.0</v>
       </c>
       <c r="BD8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.14</v>
       </c>
       <c r="BE8" s="0" t="n">
-        <v>0.0</v>
+        <v>66.67</v>
       </c>
       <c r="BF8" s="0" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="BG8" s="0" t="n">
-        <v>100.0</v>
+        <v>66.67</v>
       </c>
       <c r="BH8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="BI8" s="0" t="n">
         <v>0.0</v>
@@ -3532,55 +3532,55 @@
         <v>0.0</v>
       </c>
       <c r="BK8" s="0" t="n">
-        <v>8.94</v>
+        <v>13.79</v>
       </c>
       <c r="BL8" s="0" t="n">
-        <v>0.06</v>
+        <v>0.0</v>
       </c>
       <c r="BM8" s="0" t="n">
-        <v>0.64</v>
+        <v>0.29</v>
       </c>
       <c r="BN8" s="0" t="n">
-        <v>19.16</v>
+        <v>27.45</v>
       </c>
       <c r="BO8" s="0" t="n">
-        <v>86.58</v>
+        <v>83.6</v>
       </c>
       <c r="BP8" s="0" t="n">
-        <v>8.23</v>
+        <v>13.27</v>
       </c>
       <c r="BQ8" s="0" t="n">
-        <v>70.31</v>
+        <v>70.76</v>
       </c>
       <c r="BR8" s="0" t="n">
-        <v>0.06</v>
+        <v>0.0</v>
       </c>
       <c r="BS8" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BT8" s="0" t="n">
-        <v>9.9</v>
+        <v>11.88</v>
       </c>
       <c r="BU8" s="0" t="n">
-        <v>100.0</v>
+        <v>95.16</v>
       </c>
       <c r="BV8" s="0" t="n">
-        <v>14.01</v>
+        <v>19.93</v>
       </c>
       <c r="BW8" s="0" t="n">
-        <v>99.54</v>
+        <v>98.32</v>
       </c>
       <c r="BX8" s="0" t="n">
-        <v>5.14</v>
+        <v>7.52</v>
       </c>
       <c r="BY8" s="0" t="n">
-        <v>51.25</v>
+        <v>44.59</v>
       </c>
       <c r="BZ8" s="0" t="n">
         <v>28.77</v>
       </c>
       <c r="CA8" s="0" t="n">
-        <v>49.03</v>
+        <v>50.62</v>
       </c>
       <c r="CB8" s="0" t="n">
         <v>0.0</v>
@@ -3604,13 +3604,13 @@
         <v>0.0</v>
       </c>
       <c r="CI8" s="0" t="n">
-        <v>0.96</v>
+        <v>2.25</v>
       </c>
       <c r="CJ8" s="0" t="n">
-        <v>46.67</v>
+        <v>34.04</v>
       </c>
       <c r="CK8" s="0" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="CL8" s="0" t="n">
         <v>0.0</v>
@@ -3628,49 +3628,49 @@
         <v>0.0</v>
       </c>
       <c r="CQ8" s="0" t="n">
-        <v>3.99</v>
+        <v>5.46</v>
       </c>
       <c r="CR8" s="0" t="n">
-        <v>66.13</v>
+        <v>59.65</v>
       </c>
       <c r="CS8" s="0" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="CT8" s="0" t="n">
-        <v>1.29</v>
+        <v>1.77</v>
       </c>
       <c r="CU8" s="0" t="n">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="CV8" s="0" t="n">
-        <v>4.76</v>
+        <v>5.13</v>
       </c>
       <c r="CW8" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CX8" s="0" t="n">
-        <v>72.97</v>
+        <v>65.42</v>
       </c>
       <c r="CY8" s="0" t="n">
-        <v>20.33</v>
+        <v>33.91</v>
       </c>
       <c r="CZ8" s="0" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="DA8" s="0" t="n">
-        <v>0.33</v>
+        <v>-3.09</v>
       </c>
       <c r="DB8" s="0" t="n">
-        <v>0.021</v>
+        <v>-0.148</v>
       </c>
       <c r="DC8" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD8" s="0" t="n">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="DE8" s="0" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="DF8" s="0" t="inlineStr">
         <is>
@@ -3697,62 +3697,62 @@
         <v>0.0</v>
       </c>
       <c r="DL8" s="0" t="n">
-        <v>5646.02</v>
+        <v>5698.63</v>
       </c>
       <c r="DM8" s="0" t="n">
-        <v>51.69</v>
+        <v>86.29</v>
       </c>
       <c r="DN8" s="0" t="n">
-        <v>8.09</v>
+        <v>11.27</v>
       </c>
       <c r="DO8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.32</v>
       </c>
       <c r="DP8" s="0" t="n">
-        <v>8.09</v>
+        <v>11.58</v>
       </c>
       <c r="DQ8" s="0" t="n">
-        <v>62.73</v>
+        <v>63.32</v>
       </c>
       <c r="DR8" s="0" t="n">
-        <v>21.97</v>
+        <v>25.15</v>
       </c>
       <c r="DS8" s="0" t="n">
-        <v>64.9</v>
+        <v>60.36</v>
       </c>
       <c r="DT8" s="0" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="DU8" s="0" t="n">
-        <v>62.12</v>
+        <v>56.0</v>
       </c>
       <c r="DV8" s="0" t="n">
-        <v>7.42</v>
+        <v>4.13</v>
       </c>
       <c r="DW8" s="0" t="n">
-        <v>0.93</v>
+        <v>1.38</v>
       </c>
       <c r="DX8" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DY8" s="0" t="n">
-        <v>0.93</v>
+        <v>1.38</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>O. Ekman</t>
+          <t>J. Olsson</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Varbergs</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>Varbergs</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E9" s="0" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>175000</v>
+        <v>225000</v>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2028-12-31</t>
         </is>
       </c>
       <c r="H9" s="0" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>1392</v>
+        <v>2196</v>
       </c>
       <c r="J9" s="0" t="n">
         <v>0</v>
@@ -3790,10 +3790,10 @@
         <v>0.0</v>
       </c>
       <c r="N9" s="0" t="n">
-        <v>0.32</v>
+        <v>0.49</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="P9" s="0" t="inlineStr">
         <is>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="S9" s="0" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="T9" s="0" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="U9" s="0" t="inlineStr">
         <is>
@@ -3822,19 +3822,19 @@
         </is>
       </c>
       <c r="V9" s="0" t="n">
-        <v>0.19</v>
+        <v>0.41</v>
       </c>
       <c r="W9" s="0" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="X9" s="0" t="n">
-        <v>66.67</v>
+        <v>100.0</v>
       </c>
       <c r="Y9" s="0" t="n">
-        <v>0.0</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="AA9" s="0" t="n">
         <v>0.0</v>
@@ -3846,10 +3846,10 @@
         <v>0.0</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.06</v>
+        <v>0.37</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>0.09</v>
+        <v>0.41</v>
       </c>
       <c r="AF9" s="0" t="n">
         <v>0.0</v>
@@ -3930,7 +3930,7 @@
         <v>0.0</v>
       </c>
       <c r="BF9" s="0" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="BG9" s="0" t="n">
         <v>100.0</v>
@@ -3942,92 +3942,92 @@
         <v>0.0</v>
       </c>
       <c r="BJ9" s="0" t="n">
-        <v>0.0</v>
+        <v>0.16</v>
       </c>
       <c r="BK9" s="0" t="n">
-        <v>12.67</v>
+        <v>15.41</v>
       </c>
       <c r="BL9" s="0" t="n">
-        <v>0.39</v>
+        <v>0.53</v>
       </c>
       <c r="BM9" s="0" t="n">
-        <v>0.13</v>
+        <v>0.41</v>
       </c>
       <c r="BN9" s="0" t="n">
-        <v>22.24</v>
+        <v>26.52</v>
       </c>
       <c r="BO9" s="0" t="n">
-        <v>75.58</v>
+        <v>79.13</v>
       </c>
       <c r="BP9" s="0" t="n">
-        <v>13.77</v>
+        <v>15.45</v>
       </c>
       <c r="BQ9" s="0" t="n">
-        <v>64.79</v>
+        <v>67.64</v>
       </c>
       <c r="BR9" s="0" t="n">
-        <v>0.0</v>
+        <v>0.12</v>
       </c>
       <c r="BS9" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="BT9" s="0" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="BU9" s="0" t="n">
+        <v>95.49</v>
+      </c>
+      <c r="BV9" s="0" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="BW9" s="0" t="n">
+        <v>98.21</v>
+      </c>
+      <c r="BX9" s="0" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BY9" s="0" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="BZ9" s="0" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="CA9" s="0" t="n">
+        <v>53.36</v>
+      </c>
+      <c r="CB9" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC9" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD9" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE9" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF9" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG9" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH9" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CI9" s="0" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="CJ9" s="0" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="CK9" s="0" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CL9" s="0" t="n">
         <v>7.69</v>
       </c>
-      <c r="BU9" s="0" t="n">
-        <v>94.12</v>
-      </c>
-      <c r="BV9" s="0" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="BW9" s="0" t="n">
-        <v>96.51</v>
-      </c>
-      <c r="BX9" s="0" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="BY9" s="0" t="n">
-        <v>54.65</v>
-      </c>
-      <c r="BZ9" s="0" t="n">
-        <v>38.78</v>
-      </c>
-      <c r="CA9" s="0" t="n">
-        <v>52.27</v>
-      </c>
-      <c r="CB9" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CC9" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CD9" s="0" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="CE9" s="0" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="CF9" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CG9" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CH9" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CI9" s="0" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="CJ9" s="0" t="n">
-        <v>37.74</v>
-      </c>
-      <c r="CK9" s="0" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="CL9" s="0" t="n">
-        <v>10.0</v>
-      </c>
       <c r="CM9" s="0" t="n">
         <v>0.0</v>
       </c>
@@ -4035,55 +4035,55 @@
         <v>0.0</v>
       </c>
       <c r="CO9" s="0" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="CP9" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ9" s="0" t="n">
-        <v>9.05</v>
+        <v>7.62</v>
       </c>
       <c r="CR9" s="0" t="n">
-        <v>67.86</v>
+        <v>69.89</v>
       </c>
       <c r="CS9" s="0" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="CT9" s="0" t="n">
-        <v>1.1</v>
+        <v>2.05</v>
       </c>
       <c r="CU9" s="0" t="n">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="CV9" s="0" t="n">
-        <v>3.17</v>
+        <v>5.41</v>
       </c>
       <c r="CW9" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CX9" s="0" t="n">
-        <v>65.31</v>
+        <v>62.12</v>
       </c>
       <c r="CY9" s="0" t="n">
-        <v>17.33</v>
+        <v>41.08</v>
       </c>
       <c r="CZ9" s="0" t="n">
-        <v>1.12</v>
+        <v>1.68</v>
       </c>
       <c r="DA9" s="0" t="n">
-        <v>0.33</v>
+        <v>-8.92</v>
       </c>
       <c r="DB9" s="0" t="n">
-        <v>0.021</v>
+        <v>-0.366</v>
       </c>
       <c r="DC9" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD9" s="0" t="n">
-        <v>1.23</v>
+        <v>2.13</v>
       </c>
       <c r="DE9" s="0" t="n">
-        <v>0.0</v>
+        <v>0.2</v>
       </c>
       <c r="DF9" s="0" t="inlineStr">
         <is>
@@ -4110,62 +4110,62 @@
         <v>0.0</v>
       </c>
       <c r="DL9" s="0" t="n">
-        <v>5053.41</v>
+        <v>5696.36</v>
       </c>
       <c r="DM9" s="0" t="n">
-        <v>89.76</v>
+        <v>161.32</v>
       </c>
       <c r="DN9" s="0" t="n">
-        <v>16.19</v>
+        <v>45.56</v>
       </c>
       <c r="DO9" s="0" t="n">
-        <v>5.62</v>
+        <v>9.57</v>
       </c>
       <c r="DP9" s="0" t="n">
-        <v>21.81</v>
+        <v>55.13</v>
       </c>
       <c r="DQ9" s="0" t="n">
-        <v>56.15</v>
+        <v>63.29</v>
       </c>
       <c r="DR9" s="0" t="n">
-        <v>29.35</v>
+        <v>29.11</v>
       </c>
       <c r="DS9" s="0" t="n">
-        <v>52.37</v>
+        <v>63.54</v>
       </c>
       <c r="DT9" s="0" t="n">
-        <v>4.49</v>
+        <v>8.33</v>
       </c>
       <c r="DU9" s="0" t="n">
-        <v>50.57</v>
+        <v>65.7</v>
       </c>
       <c r="DV9" s="0" t="n">
-        <v>3.59</v>
+        <v>7.71</v>
       </c>
       <c r="DW9" s="0" t="n">
-        <v>2.09</v>
+        <v>4.01</v>
       </c>
       <c r="DX9" s="0" t="n">
-        <v>0.3</v>
+        <v>0.93</v>
       </c>
       <c r="DY9" s="0" t="n">
-        <v>2.39</v>
+        <v>4.93</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>M. Sætra</t>
+          <t>M. Pettersson</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E10" s="0" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="H10" s="0" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>1266</v>
+        <v>784</v>
       </c>
       <c r="J10" s="0" t="n">
         <v>0</v>
@@ -4203,19 +4203,19 @@
         <v>0.0</v>
       </c>
       <c r="N10" s="0" t="n">
-        <v>0.71</v>
+        <v>0.46</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>90.0</v>
+        <v>100.0</v>
       </c>
       <c r="P10" s="0" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q10" s="0" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="R10" s="0" t="inlineStr">
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="S10" s="0" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="T10" s="0" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="U10" s="0" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="V10" s="0" t="n">
-        <v>0.57</v>
+        <v>1.03</v>
       </c>
       <c r="W10" s="0" t="n">
         <v>0.0</v>
@@ -4244,7 +4244,7 @@
         <v>0.0</v>
       </c>
       <c r="Y10" s="0" t="n">
-        <v>0.36</v>
+        <v>0.11</v>
       </c>
       <c r="Z10" s="0" t="n">
         <v>100.0</v>
@@ -4259,10 +4259,10 @@
         <v>0.0</v>
       </c>
       <c r="AD10" s="0" t="n">
-        <v>0.57</v>
+        <v>1.03</v>
       </c>
       <c r="AE10" s="0" t="n">
-        <v>0.67</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" s="0" t="n">
         <v>0.0</v>
@@ -4271,7 +4271,7 @@
         <v>1</v>
       </c>
       <c r="AH10" s="0" t="n">
-        <v>0.07</v>
+        <v>0.11</v>
       </c>
       <c r="AI10" s="0" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>0.0</v>
       </c>
       <c r="AK10" s="0" t="n">
-        <v>0.14</v>
+        <v>0.0</v>
       </c>
       <c r="AL10" s="0" t="n">
         <v>0.0</v>
@@ -4337,13 +4337,13 @@
         <v>0.0</v>
       </c>
       <c r="BD10" s="0" t="n">
-        <v>0.14</v>
+        <v>0.0</v>
       </c>
       <c r="BE10" s="0" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="BF10" s="0" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="BG10" s="0" t="n">
         <v>100.0</v>
@@ -4358,55 +4358,55 @@
         <v>0.0</v>
       </c>
       <c r="BK10" s="0" t="n">
-        <v>16.49</v>
+        <v>13.89</v>
       </c>
       <c r="BL10" s="0" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="BM10" s="0" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="BN10" s="0" t="n">
-        <v>28.29</v>
+        <v>27.32</v>
       </c>
       <c r="BO10" s="0" t="n">
-        <v>80.9</v>
+        <v>78.57</v>
       </c>
       <c r="BP10" s="0" t="n">
-        <v>16.28</v>
+        <v>14.35</v>
       </c>
       <c r="BQ10" s="0" t="n">
-        <v>68.12</v>
+        <v>68.0</v>
       </c>
       <c r="BR10" s="0" t="n">
-        <v>0.07</v>
+        <v>0.11</v>
       </c>
       <c r="BS10" s="0" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="BT10" s="0" t="n">
-        <v>10.88</v>
+        <v>11.48</v>
       </c>
       <c r="BU10" s="0" t="n">
-        <v>98.04</v>
+        <v>93.0</v>
       </c>
       <c r="BV10" s="0" t="n">
-        <v>15.92</v>
+        <v>16.99</v>
       </c>
       <c r="BW10" s="0" t="n">
-        <v>97.32</v>
+        <v>97.3</v>
       </c>
       <c r="BX10" s="0" t="n">
-        <v>12.37</v>
+        <v>10.1</v>
       </c>
       <c r="BY10" s="0" t="n">
-        <v>59.77</v>
+        <v>48.86</v>
       </c>
       <c r="BZ10" s="0" t="n">
-        <v>36.72</v>
+        <v>33.08</v>
       </c>
       <c r="CA10" s="0" t="n">
-        <v>54.53</v>
+        <v>49.38</v>
       </c>
       <c r="CB10" s="0" t="n">
         <v>0.0</v>
@@ -4430,16 +4430,16 @@
         <v>0.0</v>
       </c>
       <c r="CI10" s="0" t="n">
-        <v>6.26</v>
+        <v>3.9</v>
       </c>
       <c r="CJ10" s="0" t="n">
-        <v>60.23</v>
+        <v>38.24</v>
       </c>
       <c r="CK10" s="0" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="CL10" s="0" t="n">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
       <c r="CM10" s="0" t="n">
         <v>0.0</v>
@@ -4448,55 +4448,55 @@
         <v>0.0</v>
       </c>
       <c r="CO10" s="0" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="CP10" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ10" s="0" t="n">
-        <v>8.46</v>
+        <v>7.12</v>
       </c>
       <c r="CR10" s="0" t="n">
-        <v>83.19</v>
+        <v>58.06</v>
       </c>
       <c r="CS10" s="0" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="CT10" s="0" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="CU10" s="0" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="CV10" s="0" t="n">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="CW10" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CX10" s="0" t="n">
-        <v>61.22</v>
+        <v>73.53</v>
       </c>
       <c r="CY10" s="0" t="n">
-        <v>17.6</v>
+        <v>8.86</v>
       </c>
       <c r="CZ10" s="0" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="DA10" s="0" t="n">
-        <v>-1.4</v>
+        <v>-0.14</v>
       </c>
       <c r="DB10" s="0" t="n">
-        <v>-0.1</v>
+        <v>-0.016</v>
       </c>
       <c r="DC10" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD10" s="0" t="n">
-        <v>1.71</v>
+        <v>2.53</v>
       </c>
       <c r="DE10" s="0" t="n">
-        <v>0.36</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" s="0" t="inlineStr">
         <is>
@@ -4523,62 +4523,62 @@
         <v>0.0</v>
       </c>
       <c r="DL10" s="0" t="n">
-        <v>6173.93</v>
+        <v>5681.63</v>
       </c>
       <c r="DM10" s="0" t="n">
-        <v>176.96</v>
+        <v>144.46</v>
       </c>
       <c r="DN10" s="0" t="n">
-        <v>32.43</v>
+        <v>37.97</v>
       </c>
       <c r="DO10" s="0" t="n">
-        <v>4.27</v>
+        <v>27.44</v>
       </c>
       <c r="DP10" s="0" t="n">
-        <v>36.71</v>
+        <v>65.4</v>
       </c>
       <c r="DQ10" s="0" t="n">
-        <v>68.6</v>
+        <v>63.13</v>
       </c>
       <c r="DR10" s="0" t="n">
-        <v>31.87</v>
+        <v>30.91</v>
       </c>
       <c r="DS10" s="0" t="n">
-        <v>69.15</v>
+        <v>61.42</v>
       </c>
       <c r="DT10" s="0" t="n">
-        <v>2.98</v>
+        <v>7.56</v>
       </c>
       <c r="DU10" s="0" t="n">
-        <v>65.05</v>
+        <v>55.75</v>
       </c>
       <c r="DV10" s="0" t="n">
-        <v>4.85</v>
+        <v>4.72</v>
       </c>
       <c r="DW10" s="0" t="n">
-        <v>3.73</v>
+        <v>2.83</v>
       </c>
       <c r="DX10" s="0" t="n">
-        <v>0.56</v>
+        <v>2.83</v>
       </c>
       <c r="DY10" s="0" t="n">
-        <v>4.29</v>
+        <v>5.67</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>O. Lindell</t>
+          <t>J. Ojrzyński</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -4587,21 +4587,21 @@
         </is>
       </c>
       <c r="E11" s="0" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>2027-12-29</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H11" s="0" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>1287</v>
+        <v>2461</v>
       </c>
       <c r="J11" s="0" t="n">
         <v>0</v>
@@ -4616,19 +4616,19 @@
         <v>0.0</v>
       </c>
       <c r="N11" s="0" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>70.0</v>
+        <v>82.35</v>
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="Q11" s="0" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="R11" s="0" t="inlineStr">
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="S11" s="0" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="T11" s="0" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="U11" s="0" t="inlineStr">
         <is>
@@ -4648,19 +4648,19 @@
         </is>
       </c>
       <c r="V11" s="0" t="n">
-        <v>0.84</v>
+        <v>0.44</v>
       </c>
       <c r="W11" s="0" t="n">
-        <v>0.07</v>
+        <v>0.15</v>
       </c>
       <c r="X11" s="0" t="n">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="Y11" s="0" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="Z11" s="0" t="n">
-        <v>75.0</v>
+        <v>87.5</v>
       </c>
       <c r="AA11" s="0" t="n">
         <v>0.0</v>
@@ -4672,19 +4672,19 @@
         <v>0.0</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.84</v>
+        <v>0.37</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>1.24</v>
+        <v>0.48</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.07</v>
+        <v>0.0</v>
       </c>
       <c r="AG11" s="0" t="n">
         <v>2</v>
       </c>
       <c r="AH11" s="0" t="n">
-        <v>0.14</v>
+        <v>0.07</v>
       </c>
       <c r="AI11" s="0" t="n">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>0.0</v>
       </c>
       <c r="BF11" s="0" t="n">
-        <v>0.35</v>
+        <v>0.11</v>
       </c>
       <c r="BG11" s="0" t="n">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="BH11" s="0" t="n">
         <v>0.0</v>
@@ -4768,89 +4768,89 @@
         <v>0.0</v>
       </c>
       <c r="BJ11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK11" s="0" t="n">
+        <v>9.47</v>
+      </c>
+      <c r="BL11" s="0" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BM11" s="0" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BN11" s="0" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="BO11" s="0" t="n">
+        <v>84.24</v>
+      </c>
+      <c r="BP11" s="0" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="BQ11" s="0" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="BR11" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BS11" s="0" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="BT11" s="0" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="BU11" s="0" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="BV11" s="0" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="BW11" s="0" t="n">
+        <v>98.94</v>
+      </c>
+      <c r="BX11" s="0" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="BY11" s="0" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="BZ11" s="0" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="CA11" s="0" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="CB11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI11" s="0" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CJ11" s="0" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="CK11" s="0" t="n">
         <v>0.07</v>
       </c>
-      <c r="BK11" s="0" t="n">
-        <v>23.08</v>
-      </c>
-      <c r="BL11" s="0" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="BM11" s="0" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="BN11" s="0" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="BO11" s="0" t="n">
-        <v>87.22</v>
-      </c>
-      <c r="BP11" s="0" t="n">
-        <v>17.27</v>
-      </c>
-      <c r="BQ11" s="0" t="n">
-        <v>76.92</v>
-      </c>
-      <c r="BR11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT11" s="0" t="n">
-        <v>18.32</v>
-      </c>
-      <c r="BU11" s="0" t="n">
-        <v>96.56</v>
-      </c>
-      <c r="BV11" s="0" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="BW11" s="0" t="n">
-        <v>99.0</v>
-      </c>
-      <c r="BX11" s="0" t="n">
-        <v>8.88</v>
-      </c>
-      <c r="BY11" s="0" t="n">
-        <v>51.97</v>
-      </c>
-      <c r="BZ11" s="0" t="n">
-        <v>26.03</v>
-      </c>
-      <c r="CA11" s="0" t="n">
-        <v>47.74</v>
-      </c>
-      <c r="CB11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CC11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CD11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CE11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CF11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CG11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CH11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CI11" s="0" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CJ11" s="0" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="CK11" s="0" t="n">
-        <v>0.35</v>
-      </c>
       <c r="CL11" s="0" t="n">
         <v>0.0</v>
       </c>
@@ -4867,49 +4867,49 @@
         <v>0.0</v>
       </c>
       <c r="CQ11" s="0" t="n">
-        <v>6.29</v>
+        <v>4.17</v>
       </c>
       <c r="CR11" s="0" t="n">
-        <v>64.44</v>
+        <v>63.16</v>
       </c>
       <c r="CS11" s="0" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="CT11" s="0" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="CU11" s="0" t="n">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="CV11" s="0" t="n">
-        <v>4.13</v>
+        <v>4.86</v>
       </c>
       <c r="CW11" s="0" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CX11" s="0" t="n">
-        <v>67.8</v>
+        <v>70.68</v>
       </c>
       <c r="CY11" s="0" t="n">
-        <v>19.17</v>
+        <v>35.57</v>
       </c>
       <c r="CZ11" s="0" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="DA11" s="0" t="n">
-        <v>0.17</v>
+        <v>-3.43</v>
       </c>
       <c r="DB11" s="0" t="n">
-        <v>0.012</v>
+        <v>-0.125</v>
       </c>
       <c r="DC11" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="DD11" s="0" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="DE11" s="0" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="DF11" s="0" t="inlineStr">
         <is>
@@ -4936,62 +4936,62 @@
         <v>0.0</v>
       </c>
       <c r="DL11" s="0" t="n">
-        <v>5777.23</v>
+        <v>5646.02</v>
       </c>
       <c r="DM11" s="0" t="n">
-        <v>87.24</v>
+        <v>51.69</v>
       </c>
       <c r="DN11" s="0" t="n">
-        <v>26.98</v>
+        <v>8.09</v>
       </c>
       <c r="DO11" s="0" t="n">
-        <v>2.16</v>
+        <v>0.0</v>
       </c>
       <c r="DP11" s="0" t="n">
-        <v>29.14</v>
+        <v>8.09</v>
       </c>
       <c r="DQ11" s="0" t="n">
-        <v>64.19</v>
+        <v>62.73</v>
       </c>
       <c r="DR11" s="0" t="n">
-        <v>26.8</v>
+        <v>21.97</v>
       </c>
       <c r="DS11" s="0" t="n">
-        <v>60.42</v>
+        <v>64.9</v>
       </c>
       <c r="DT11" s="0" t="n">
-        <v>6.73</v>
+        <v>2.78</v>
       </c>
       <c r="DU11" s="0" t="n">
-        <v>65.01</v>
+        <v>62.12</v>
       </c>
       <c r="DV11" s="0" t="n">
-        <v>6.58</v>
+        <v>7.42</v>
       </c>
       <c r="DW11" s="0" t="n">
-        <v>2.6</v>
+        <v>0.93</v>
       </c>
       <c r="DX11" s="0" t="n">
-        <v>0.15</v>
+        <v>0.0</v>
       </c>
       <c r="DY11" s="0" t="n">
-        <v>2.75</v>
+        <v>0.93</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>L. Eriksson</t>
+          <t>G. Lillienberg</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -5007,14 +5007,14 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H12" s="0" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>1397</v>
+        <v>867</v>
       </c>
       <c r="J12" s="0" t="n">
         <v>0</v>
@@ -5023,16 +5023,16 @@
         <v>0.0</v>
       </c>
       <c r="L12" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="0" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>66.67</v>
+        <v>100.0</v>
       </c>
       <c r="P12" s="0" t="inlineStr">
         <is>
@@ -5046,14 +5046,14 @@
       </c>
       <c r="R12" s="0" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S12" s="0" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="T12" s="0" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="U12" s="0" t="inlineStr">
         <is>
@@ -5061,19 +5061,19 @@
         </is>
       </c>
       <c r="V12" s="0" t="n">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
       <c r="W12" s="0" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="X12" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="Y12" s="0" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="AA12" s="0" t="n">
         <v>0.0</v>
@@ -5085,10 +5085,10 @@
         <v>0.0</v>
       </c>
       <c r="AD12" s="0" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="AE12" s="0" t="n">
-        <v>0.38</v>
+        <v>0.63</v>
       </c>
       <c r="AF12" s="0" t="n">
         <v>0.0</v>
@@ -5106,7 +5106,7 @@
         <v>0.0</v>
       </c>
       <c r="AK12" s="0" t="n">
-        <v>0.06</v>
+        <v>0.0</v>
       </c>
       <c r="AL12" s="0" t="n">
         <v>0.0</v>
@@ -5139,7 +5139,7 @@
         <v>0.0</v>
       </c>
       <c r="AV12" s="0" t="n">
-        <v>0.06</v>
+        <v>0.0</v>
       </c>
       <c r="AW12" s="0" t="n">
         <v>0.0</v>
@@ -5163,13 +5163,13 @@
         <v>0.0</v>
       </c>
       <c r="BD12" s="0" t="n">
-        <v>0.06</v>
+        <v>0.0</v>
       </c>
       <c r="BE12" s="0" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="BF12" s="0" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="BG12" s="0" t="n">
         <v>100.0</v>
@@ -5184,25 +5184,25 @@
         <v>0.0</v>
       </c>
       <c r="BK12" s="0" t="n">
-        <v>17.2</v>
+        <v>17.54</v>
       </c>
       <c r="BL12" s="0" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="BM12" s="0" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="BN12" s="0" t="n">
-        <v>29.06</v>
+        <v>26.47</v>
       </c>
       <c r="BO12" s="0" t="n">
-        <v>77.83</v>
+        <v>87.84</v>
       </c>
       <c r="BP12" s="0" t="n">
-        <v>19.39</v>
+        <v>10.8</v>
       </c>
       <c r="BQ12" s="0" t="n">
-        <v>68.44</v>
+        <v>73.08</v>
       </c>
       <c r="BR12" s="0" t="n">
         <v>0.0</v>
@@ -5211,28 +5211,28 @@
         <v>0.0</v>
       </c>
       <c r="BT12" s="0" t="n">
-        <v>9.47</v>
+        <v>14.22</v>
       </c>
       <c r="BU12" s="0" t="n">
-        <v>96.6</v>
+        <v>98.54</v>
       </c>
       <c r="BV12" s="0" t="n">
-        <v>15.4</v>
+        <v>19.62</v>
       </c>
       <c r="BW12" s="0" t="n">
-        <v>97.91</v>
+        <v>98.94</v>
       </c>
       <c r="BX12" s="0" t="n">
-        <v>13.59</v>
+        <v>6.85</v>
       </c>
       <c r="BY12" s="0" t="n">
-        <v>55.45</v>
+        <v>56.06</v>
       </c>
       <c r="BZ12" s="0" t="n">
-        <v>39.7</v>
+        <v>29.98</v>
       </c>
       <c r="CA12" s="0" t="n">
-        <v>55.97</v>
+        <v>46.02</v>
       </c>
       <c r="CB12" s="0" t="n">
         <v>0.0</v>
@@ -5244,7 +5244,7 @@
         <v>0.0</v>
       </c>
       <c r="CE12" s="0" t="n">
-        <v>0.06</v>
+        <v>0.0</v>
       </c>
       <c r="CF12" s="0" t="n">
         <v>0.0</v>
@@ -5256,73 +5256,73 @@
         <v>0.0</v>
       </c>
       <c r="CI12" s="0" t="n">
-        <v>6.12</v>
+        <v>2.08</v>
       </c>
       <c r="CJ12" s="0" t="n">
-        <v>52.63</v>
+        <v>60.0</v>
       </c>
       <c r="CK12" s="0" t="n">
-        <v>0.77</v>
+        <v>0.1</v>
       </c>
       <c r="CL12" s="0" t="n">
-        <v>25.0</v>
+        <v>100.0</v>
       </c>
       <c r="CM12" s="0" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="CN12" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="CO12" s="0" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="CP12" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ12" s="0" t="n">
-        <v>9.99</v>
+        <v>5.81</v>
       </c>
       <c r="CR12" s="0" t="n">
-        <v>79.35</v>
+        <v>66.07</v>
       </c>
       <c r="CS12" s="0" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="CT12" s="0" t="n">
-        <v>1.16</v>
+        <v>0.83</v>
       </c>
       <c r="CU12" s="0" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="CV12" s="0" t="n">
-        <v>3.8</v>
+        <v>3.63</v>
       </c>
       <c r="CW12" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CX12" s="0" t="n">
-        <v>69.49</v>
+        <v>77.14</v>
       </c>
       <c r="CY12" s="0" t="n">
-        <v>18.39</v>
+        <v>10.15</v>
       </c>
       <c r="CZ12" s="0" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="DA12" s="0" t="n">
-        <v>0.39</v>
+        <v>2.15</v>
       </c>
       <c r="DB12" s="0" t="n">
-        <v>0.025</v>
+        <v>0.223</v>
       </c>
       <c r="DC12" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD12" s="0" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DE12" s="0" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="DF12" s="0" t="inlineStr">
         <is>
@@ -5349,62 +5349,62 @@
         <v>0.0</v>
       </c>
       <c r="DL12" s="0" t="n">
-        <v>5551.2</v>
+        <v>5557.82</v>
       </c>
       <c r="DM12" s="0" t="n">
-        <v>110.97</v>
+        <v>119.65</v>
       </c>
       <c r="DN12" s="0" t="n">
-        <v>18.35</v>
+        <v>25.78</v>
       </c>
       <c r="DO12" s="0" t="n">
-        <v>2.27</v>
+        <v>4.9</v>
       </c>
       <c r="DP12" s="0" t="n">
-        <v>20.61</v>
+        <v>30.68</v>
       </c>
       <c r="DQ12" s="0" t="n">
-        <v>61.68</v>
+        <v>61.75</v>
       </c>
       <c r="DR12" s="0" t="n">
-        <v>27.26</v>
+        <v>29.32</v>
       </c>
       <c r="DS12" s="0" t="n">
-        <v>54.25</v>
+        <v>61.0</v>
       </c>
       <c r="DT12" s="0" t="n">
-        <v>4.24</v>
+        <v>6.86</v>
       </c>
       <c r="DU12" s="0" t="n">
-        <v>60.01</v>
+        <v>65.08</v>
       </c>
       <c r="DV12" s="0" t="n">
-        <v>3.03</v>
+        <v>7.42</v>
       </c>
       <c r="DW12" s="0" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="DX12" s="0" t="n">
-        <v>0.3</v>
+        <v>0.74</v>
       </c>
       <c r="DY12" s="0" t="n">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>G. Lillienberg</t>
+          <t>L. Eriksson</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E13" s="0" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="H13" s="0" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>484</v>
+        <v>2460</v>
       </c>
       <c r="J13" s="0" t="n">
         <v>0</v>
@@ -5436,153 +5436,153 @@
         <v>0.0</v>
       </c>
       <c r="L13" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="0" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="O13" s="0" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="P13" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="Q13" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="R13" s="0" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="V13" s="0" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="W13" s="0" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="X13" s="0" t="n">
         <v>100.0</v>
       </c>
-      <c r="P13" s="0" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="Q13" s="0" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="R13" s="0" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="S13" s="0" t="n">
-        <v>186</v>
-      </c>
-      <c r="T13" s="0" t="n">
-        <v>74</v>
-      </c>
-      <c r="U13" s="0" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="V13" s="0" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="W13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="X13" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="Y13" s="0" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="Z13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD13" s="0" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AE13" s="0" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AF13" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK13" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AL13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AT13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV13" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AW13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD13" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BE13" s="0" t="n">
         <v>100.0</v>
       </c>
-      <c r="AA13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD13" s="0" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AE13" s="0" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="AF13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AO13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AP13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AR13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AT13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AU13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AV13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AW13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AX13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AY13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AZ13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BA13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BB13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BC13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BD13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BE13" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="BF13" s="0" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="BG13" s="0" t="n">
         <v>100.0</v>
@@ -5597,55 +5597,55 @@
         <v>0.0</v>
       </c>
       <c r="BK13" s="0" t="n">
-        <v>18.97</v>
+        <v>17.3</v>
       </c>
       <c r="BL13" s="0" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="BM13" s="0" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="BN13" s="0" t="n">
-        <v>27.33</v>
+        <v>29.05</v>
       </c>
       <c r="BO13" s="0" t="n">
-        <v>87.76</v>
+        <v>75.31</v>
       </c>
       <c r="BP13" s="0" t="n">
-        <v>10.79</v>
+        <v>20.34</v>
       </c>
       <c r="BQ13" s="0" t="n">
-        <v>70.69</v>
+        <v>66.73</v>
       </c>
       <c r="BR13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BS13" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="BT13" s="0" t="n">
-        <v>14.88</v>
+        <v>8.3</v>
       </c>
       <c r="BU13" s="0" t="n">
-        <v>100.0</v>
+        <v>96.04</v>
       </c>
       <c r="BV13" s="0" t="n">
-        <v>20.64</v>
+        <v>14.93</v>
       </c>
       <c r="BW13" s="0" t="n">
-        <v>99.1</v>
+        <v>96.32</v>
       </c>
       <c r="BX13" s="0" t="n">
-        <v>6.69</v>
+        <v>14.09</v>
       </c>
       <c r="BY13" s="0" t="n">
-        <v>52.78</v>
+        <v>53.25</v>
       </c>
       <c r="BZ13" s="0" t="n">
-        <v>30.28</v>
+        <v>39.11</v>
       </c>
       <c r="CA13" s="0" t="n">
-        <v>42.55</v>
+        <v>54.86</v>
       </c>
       <c r="CB13" s="0" t="n">
         <v>0.0</v>
@@ -5657,7 +5657,7 @@
         <v>0.0</v>
       </c>
       <c r="CE13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.07</v>
       </c>
       <c r="CF13" s="0" t="n">
         <v>0.0</v>
@@ -5669,73 +5669,73 @@
         <v>0.0</v>
       </c>
       <c r="CI13" s="0" t="n">
-        <v>2.05</v>
+        <v>5.67</v>
       </c>
       <c r="CJ13" s="0" t="n">
-        <v>54.55</v>
+        <v>45.16</v>
       </c>
       <c r="CK13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.73</v>
       </c>
       <c r="CL13" s="0" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="CM13" s="0" t="n">
-        <v>0.19</v>
+        <v>0.07</v>
       </c>
       <c r="CN13" s="0" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="CO13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.15</v>
       </c>
       <c r="CP13" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ13" s="0" t="n">
-        <v>5.58</v>
+        <v>10.28</v>
       </c>
       <c r="CR13" s="0" t="n">
-        <v>66.67</v>
+        <v>76.16</v>
       </c>
       <c r="CS13" s="0" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="CT13" s="0" t="n">
-        <v>0.74</v>
+        <v>1.32</v>
       </c>
       <c r="CU13" s="0" t="n">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="CV13" s="0" t="n">
-        <v>3.72</v>
+        <v>4.17</v>
       </c>
       <c r="CW13" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CX13" s="0" t="n">
-        <v>80.0</v>
+        <v>68.42</v>
       </c>
       <c r="CY13" s="0" t="n">
-        <v>6.31</v>
+        <v>35.24</v>
       </c>
       <c r="CZ13" s="0" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="DA13" s="0" t="n">
-        <v>2.31</v>
+        <v>-0.76</v>
       </c>
       <c r="DB13" s="0" t="n">
-        <v>0.43</v>
+        <v>-0.028</v>
       </c>
       <c r="DC13" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD13" s="0" t="n">
-        <v>0.93</v>
+        <v>1.43</v>
       </c>
       <c r="DE13" s="0" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="DF13" s="0" t="inlineStr">
         <is>
@@ -5762,62 +5762,62 @@
         <v>0.0</v>
       </c>
       <c r="DL13" s="0" t="n">
-        <v>6006.01</v>
+        <v>5551.2</v>
       </c>
       <c r="DM13" s="0" t="n">
-        <v>142.83</v>
+        <v>110.97</v>
       </c>
       <c r="DN13" s="0" t="n">
-        <v>32.1</v>
+        <v>18.35</v>
       </c>
       <c r="DO13" s="0" t="n">
-        <v>6.1</v>
+        <v>2.27</v>
       </c>
       <c r="DP13" s="0" t="n">
-        <v>38.2</v>
+        <v>20.61</v>
       </c>
       <c r="DQ13" s="0" t="n">
-        <v>66.73</v>
+        <v>61.68</v>
       </c>
       <c r="DR13" s="0" t="n">
-        <v>29.32</v>
+        <v>27.26</v>
       </c>
       <c r="DS13" s="0" t="n">
-        <v>60.72</v>
+        <v>54.25</v>
       </c>
       <c r="DT13" s="0" t="n">
-        <v>5.54</v>
+        <v>4.24</v>
       </c>
       <c r="DU13" s="0" t="n">
-        <v>65.1</v>
+        <v>60.01</v>
       </c>
       <c r="DV13" s="0" t="n">
-        <v>6.93</v>
+        <v>3.03</v>
       </c>
       <c r="DW13" s="0" t="n">
-        <v>3.23</v>
+        <v>2.42</v>
       </c>
       <c r="DX13" s="0" t="n">
-        <v>0.92</v>
+        <v>0.3</v>
       </c>
       <c r="DY13" s="0" t="n">
-        <v>4.16</v>
+        <v>2.73</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>A. Andersson</t>
+          <t>W. Eskelinen</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -5826,21 +5826,21 @@
         </is>
       </c>
       <c r="E14" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t/>
         </is>
       </c>
       <c r="H14" s="0" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>756</v>
+        <v>1355</v>
       </c>
       <c r="J14" s="0" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="0" t="n">
-        <v>0.48</v>
+        <v>0.07</v>
       </c>
       <c r="O14" s="0" t="n">
         <v>100.0</v>
@@ -5872,14 +5872,14 @@
       </c>
       <c r="R14" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>right</t>
         </is>
       </c>
       <c r="S14" s="0" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="T14" s="0" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U14" s="0" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="V14" s="0" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="W14" s="0" t="n">
         <v>0.0</v>
@@ -5896,10 +5896,10 @@
         <v>0.0</v>
       </c>
       <c r="Y14" s="0" t="n">
-        <v>0.12</v>
+        <v>0.0</v>
       </c>
       <c r="Z14" s="0" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA14" s="0" t="n">
         <v>0.0</v>
@@ -5911,10 +5911,10 @@
         <v>0.0</v>
       </c>
       <c r="AD14" s="0" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="AE14" s="0" t="n">
-        <v>0.15</v>
+        <v>0.53</v>
       </c>
       <c r="AF14" s="0" t="n">
         <v>0.0</v>
@@ -5932,7 +5932,7 @@
         <v>0.0</v>
       </c>
       <c r="AK14" s="0" t="n">
-        <v>0.12</v>
+        <v>0.0</v>
       </c>
       <c r="AL14" s="0" t="n">
         <v>0.0</v>
@@ -5989,13 +5989,13 @@
         <v>0.0</v>
       </c>
       <c r="BD14" s="0" t="n">
-        <v>0.12</v>
+        <v>0.0</v>
       </c>
       <c r="BE14" s="0" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="BF14" s="0" t="n">
-        <v>0.24</v>
+        <v>0.07</v>
       </c>
       <c r="BG14" s="0" t="n">
         <v>100.0</v>
@@ -6010,25 +6010,25 @@
         <v>0.0</v>
       </c>
       <c r="BK14" s="0" t="n">
-        <v>19.64</v>
+        <v>12.22</v>
       </c>
       <c r="BL14" s="0" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="BM14" s="0" t="n">
-        <v>0.36</v>
+        <v>0.07</v>
       </c>
       <c r="BN14" s="0" t="n">
-        <v>30.71</v>
+        <v>20.72</v>
       </c>
       <c r="BO14" s="0" t="n">
-        <v>75.97</v>
+        <v>77.56</v>
       </c>
       <c r="BP14" s="0" t="n">
-        <v>16.19</v>
+        <v>12.15</v>
       </c>
       <c r="BQ14" s="0" t="n">
-        <v>58.09</v>
+        <v>65.57</v>
       </c>
       <c r="BR14" s="0" t="n">
         <v>0.0</v>
@@ -6037,28 +6037,28 @@
         <v>0.0</v>
       </c>
       <c r="BT14" s="0" t="n">
-        <v>12.98</v>
+        <v>7.77</v>
       </c>
       <c r="BU14" s="0" t="n">
-        <v>96.33</v>
+        <v>94.87</v>
       </c>
       <c r="BV14" s="0" t="n">
-        <v>16.9</v>
+        <v>11.76</v>
       </c>
       <c r="BW14" s="0" t="n">
-        <v>97.18</v>
+        <v>96.05</v>
       </c>
       <c r="BX14" s="0" t="n">
-        <v>13.81</v>
+        <v>8.97</v>
       </c>
       <c r="BY14" s="0" t="n">
-        <v>50.0</v>
+        <v>53.33</v>
       </c>
       <c r="BZ14" s="0" t="n">
-        <v>37.75</v>
+        <v>35.84</v>
       </c>
       <c r="CA14" s="0" t="n">
-        <v>52.5</v>
+        <v>51.32</v>
       </c>
       <c r="CB14" s="0" t="n">
         <v>0.0</v>
@@ -6082,16 +6082,16 @@
         <v>0.0</v>
       </c>
       <c r="CI14" s="0" t="n">
-        <v>4.52</v>
+        <v>2.99</v>
       </c>
       <c r="CJ14" s="0" t="n">
-        <v>50.0</v>
+        <v>44.44</v>
       </c>
       <c r="CK14" s="0" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="CL14" s="0" t="n">
-        <v>0.0</v>
+        <v>33.33</v>
       </c>
       <c r="CM14" s="0" t="n">
         <v>0.0</v>
@@ -6100,55 +6100,55 @@
         <v>0.0</v>
       </c>
       <c r="CO14" s="0" t="n">
-        <v>0.0</v>
+        <v>0.07</v>
       </c>
       <c r="CP14" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ14" s="0" t="n">
-        <v>10.12</v>
+        <v>7.24</v>
       </c>
       <c r="CR14" s="0" t="n">
-        <v>63.53</v>
+        <v>68.81</v>
       </c>
       <c r="CS14" s="0" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="CT14" s="0" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="CU14" s="0" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="CV14" s="0" t="n">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="CW14" s="0" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CX14" s="0" t="n">
-        <v>64.52</v>
+        <v>63.16</v>
       </c>
       <c r="CY14" s="0" t="n">
-        <v>9.36</v>
+        <v>15.95</v>
       </c>
       <c r="CZ14" s="0" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="DA14" s="0" t="n">
-        <v>-1.64</v>
+        <v>-5.05</v>
       </c>
       <c r="DB14" s="0" t="n">
-        <v>-0.195</v>
+        <v>-0.335</v>
       </c>
       <c r="DC14" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD14" s="0" t="n">
-        <v>2.86</v>
+        <v>1.53</v>
       </c>
       <c r="DE14" s="0" t="n">
-        <v>0.12</v>
+        <v>0.0</v>
       </c>
       <c r="DF14" s="0" t="inlineStr">
         <is>
@@ -6175,62 +6175,62 @@
         <v>0.0</v>
       </c>
       <c r="DL14" s="0" t="n">
-        <v>10969.78</v>
+        <v>5543.65</v>
       </c>
       <c r="DM14" s="0" t="n">
-        <v>1721.24</v>
+        <v>76.46</v>
       </c>
       <c r="DN14" s="0" t="n">
-        <v>582.28</v>
+        <v>17.27</v>
       </c>
       <c r="DO14" s="0" t="n">
-        <v>222.34</v>
+        <v>1.53</v>
       </c>
       <c r="DP14" s="0" t="n">
-        <v>804.61</v>
+        <v>18.8</v>
       </c>
       <c r="DQ14" s="0" t="n">
-        <v>121.89</v>
+        <v>61.6</v>
       </c>
       <c r="DR14" s="0" t="n">
-        <v>33.26</v>
+        <v>29.04</v>
       </c>
       <c r="DS14" s="0" t="n">
-        <v>210.7</v>
+        <v>45.09</v>
       </c>
       <c r="DT14" s="0" t="n">
-        <v>30.82</v>
+        <v>5.04</v>
       </c>
       <c r="DU14" s="0" t="n">
-        <v>174.32</v>
+        <v>50.58</v>
       </c>
       <c r="DV14" s="0" t="n">
-        <v>35.88</v>
+        <v>6.18</v>
       </c>
       <c r="DW14" s="0" t="n">
-        <v>46.99</v>
+        <v>1.83</v>
       </c>
       <c r="DX14" s="0" t="n">
-        <v>15.16</v>
+        <v>0.23</v>
       </c>
       <c r="DY14" s="0" t="n">
-        <v>62.15</v>
+        <v>2.06</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>M. Pettersson</t>
+          <t>V. Frodig</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -6239,36 +6239,36 @@
         </is>
       </c>
       <c r="E15" s="0" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H15" s="0" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>395</v>
+        <v>2161</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.0</v>
+        <v>0.29</v>
       </c>
       <c r="L15" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="N15" s="0" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="O15" s="0" t="n">
         <v>100.0</v>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="S15" s="0" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="T15" s="0" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="U15" s="0" t="inlineStr">
         <is>
@@ -6300,16 +6300,16 @@
         </is>
       </c>
       <c r="V15" s="0" t="n">
-        <v>1.37</v>
+        <v>0.75</v>
       </c>
       <c r="W15" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="X15" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="Y15" s="0" t="n">
-        <v>0.23</v>
+        <v>0.08</v>
       </c>
       <c r="Z15" s="0" t="n">
         <v>100.0</v>
@@ -6324,61 +6324,61 @@
         <v>0.0</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>1.37</v>
+        <v>0.71</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>1.86</v>
+        <v>0.89</v>
       </c>
       <c r="AF15" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="AG15" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="0" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AI15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK15" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AL15" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AM15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AH15" s="0" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AI15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM15" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="AN15" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AO15" s="0" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
       <c r="AP15" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ15" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AR15" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS15" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AT15" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="AU15" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="AV15" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AW15" s="0" t="n">
         <v>0.0</v>
@@ -6408,70 +6408,70 @@
         <v>0.0</v>
       </c>
       <c r="BF15" s="0" t="n">
-        <v>0.46</v>
+        <v>0.29</v>
       </c>
       <c r="BG15" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="BH15" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BI15" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BJ15" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BK15" s="0" t="n">
-        <v>10.25</v>
+        <v>10.58</v>
       </c>
       <c r="BL15" s="0" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="BM15" s="0" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="BN15" s="0" t="n">
-        <v>25.97</v>
+        <v>19.99</v>
       </c>
       <c r="BO15" s="0" t="n">
-        <v>78.95</v>
+        <v>80.21</v>
       </c>
       <c r="BP15" s="0" t="n">
-        <v>11.85</v>
+        <v>11.49</v>
       </c>
       <c r="BQ15" s="0" t="n">
-        <v>65.38</v>
+        <v>70.29</v>
       </c>
       <c r="BR15" s="0" t="n">
-        <v>0.23</v>
+        <v>0.0</v>
       </c>
       <c r="BS15" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BT15" s="0" t="n">
-        <v>12.3</v>
+        <v>7.33</v>
       </c>
       <c r="BU15" s="0" t="n">
-        <v>94.44</v>
+        <v>93.18</v>
       </c>
       <c r="BV15" s="0" t="n">
-        <v>17.32</v>
+        <v>13.16</v>
       </c>
       <c r="BW15" s="0" t="n">
-        <v>98.68</v>
+        <v>96.52</v>
       </c>
       <c r="BX15" s="0" t="n">
-        <v>8.43</v>
+        <v>6.83</v>
       </c>
       <c r="BY15" s="0" t="n">
-        <v>40.54</v>
+        <v>48.78</v>
       </c>
       <c r="BZ15" s="0" t="n">
-        <v>32.67</v>
+        <v>32.16</v>
       </c>
       <c r="CA15" s="0" t="n">
-        <v>49.47</v>
+        <v>51.27</v>
       </c>
       <c r="CB15" s="0" t="n">
         <v>0.0</v>
@@ -6492,19 +6492,19 @@
         <v>0.0</v>
       </c>
       <c r="CH15" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="CI15" s="0" t="n">
-        <v>3.65</v>
+        <v>2.33</v>
       </c>
       <c r="CJ15" s="0" t="n">
-        <v>31.25</v>
+        <v>30.36</v>
       </c>
       <c r="CK15" s="0" t="n">
-        <v>1.14</v>
+        <v>0.37</v>
       </c>
       <c r="CL15" s="0" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="CM15" s="0" t="n">
         <v>0.0</v>
@@ -6513,55 +6513,55 @@
         <v>0.0</v>
       </c>
       <c r="CO15" s="0" t="n">
-        <v>0.23</v>
+        <v>0.0</v>
       </c>
       <c r="CP15" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ15" s="0" t="n">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
       <c r="CR15" s="0" t="n">
-        <v>50.0</v>
+        <v>61.83</v>
       </c>
       <c r="CS15" s="0" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="CT15" s="0" t="n">
-        <v>1.14</v>
+        <v>1.67</v>
       </c>
       <c r="CU15" s="0" t="n">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="CV15" s="0" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="CW15" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CX15" s="0" t="n">
-        <v>73.68</v>
+        <v>60.78</v>
       </c>
       <c r="CY15" s="0" t="n">
-        <v>3.85</v>
+        <v>35.07</v>
       </c>
       <c r="CZ15" s="0" t="n">
-        <v>0.88</v>
+        <v>1.46</v>
       </c>
       <c r="DA15" s="0" t="n">
-        <v>-1.15</v>
+        <v>-4.93</v>
       </c>
       <c r="DB15" s="0" t="n">
-        <v>-0.262</v>
+        <v>-0.205</v>
       </c>
       <c r="DC15" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD15" s="0" t="n">
-        <v>2.73</v>
+        <v>2.33</v>
       </c>
       <c r="DE15" s="0" t="n">
-        <v>0.23</v>
+        <v>0.08</v>
       </c>
       <c r="DF15" s="0" t="inlineStr">
         <is>
@@ -6588,46 +6588,46 @@
         <v>0.0</v>
       </c>
       <c r="DL15" s="0" t="n">
-        <v>5681.63</v>
+        <v>5414.59</v>
       </c>
       <c r="DM15" s="0" t="n">
-        <v>144.46</v>
+        <v>93.61</v>
       </c>
       <c r="DN15" s="0" t="n">
-        <v>37.97</v>
+        <v>19.78</v>
       </c>
       <c r="DO15" s="0" t="n">
-        <v>27.44</v>
+        <v>5.68</v>
       </c>
       <c r="DP15" s="0" t="n">
-        <v>65.4</v>
+        <v>25.47</v>
       </c>
       <c r="DQ15" s="0" t="n">
-        <v>63.13</v>
+        <v>60.16</v>
       </c>
       <c r="DR15" s="0" t="n">
-        <v>30.91</v>
+        <v>26.49</v>
       </c>
       <c r="DS15" s="0" t="n">
-        <v>61.42</v>
+        <v>58.25</v>
       </c>
       <c r="DT15" s="0" t="n">
-        <v>7.56</v>
+        <v>3.16</v>
       </c>
       <c r="DU15" s="0" t="n">
-        <v>55.75</v>
+        <v>62.31</v>
       </c>
       <c r="DV15" s="0" t="n">
-        <v>4.72</v>
+        <v>3.16</v>
       </c>
       <c r="DW15" s="0" t="n">
-        <v>2.83</v>
+        <v>3.16</v>
       </c>
       <c r="DX15" s="0" t="n">
-        <v>2.83</v>
+        <v>0.45</v>
       </c>
       <c r="DY15" s="0" t="n">
-        <v>5.67</v>
+        <v>3.61</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="16">
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="E16" s="0" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>0</v>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="H16" s="0" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>1228</v>
+        <v>2293</v>
       </c>
       <c r="J16" s="0" t="n">
         <v>0</v>
@@ -6681,7 +6681,7 @@
         <v>0.0</v>
       </c>
       <c r="N16" s="0" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="O16" s="0" t="n">
         <v>100.0</v>
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="V16" s="0" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="W16" s="0" t="n">
         <v>0.0</v>
@@ -6722,7 +6722,7 @@
         <v>0.0</v>
       </c>
       <c r="Y16" s="0" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="Z16" s="0" t="n">
         <v>100.0</v>
@@ -6737,10 +6737,10 @@
         <v>0.0</v>
       </c>
       <c r="AD16" s="0" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="AE16" s="0" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="AF16" s="0" t="n">
         <v>0.0</v>
@@ -6791,7 +6791,7 @@
         <v>0.0</v>
       </c>
       <c r="AV16" s="0" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="AW16" s="0" t="n">
         <v>0.0</v>
@@ -6821,10 +6821,10 @@
         <v>0.0</v>
       </c>
       <c r="BF16" s="0" t="n">
-        <v>0.0</v>
+        <v>0.12</v>
       </c>
       <c r="BG16" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="BH16" s="0" t="n">
         <v>0.0</v>
@@ -6833,58 +6833,58 @@
         <v>0.0</v>
       </c>
       <c r="BJ16" s="0" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="BK16" s="0" t="n">
-        <v>16.64</v>
+        <v>15.62</v>
       </c>
       <c r="BL16" s="0" t="n">
-        <v>0.07</v>
+        <v>0.2</v>
       </c>
       <c r="BM16" s="0" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BN16" s="0" t="n">
-        <v>27.78</v>
+        <v>26.02</v>
       </c>
       <c r="BO16" s="0" t="n">
-        <v>86.28</v>
+        <v>85.52</v>
       </c>
       <c r="BP16" s="0" t="n">
-        <v>11.07</v>
+        <v>11.3</v>
       </c>
       <c r="BQ16" s="0" t="n">
-        <v>72.19</v>
+        <v>73.26</v>
       </c>
       <c r="BR16" s="0" t="n">
-        <v>0.0</v>
+        <v>0.08</v>
       </c>
       <c r="BS16" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="BT16" s="0" t="n">
-        <v>14.73</v>
+        <v>13.19</v>
       </c>
       <c r="BU16" s="0" t="n">
-        <v>96.02</v>
+        <v>94.94</v>
       </c>
       <c r="BV16" s="0" t="n">
-        <v>22.57</v>
+        <v>20.14</v>
       </c>
       <c r="BW16" s="0" t="n">
-        <v>98.7</v>
+        <v>97.66</v>
       </c>
       <c r="BX16" s="0" t="n">
-        <v>5.2</v>
+        <v>5.89</v>
       </c>
       <c r="BY16" s="0" t="n">
-        <v>32.39</v>
+        <v>44.0</v>
       </c>
       <c r="BZ16" s="0" t="n">
-        <v>26.32</v>
+        <v>26.94</v>
       </c>
       <c r="CA16" s="0" t="n">
-        <v>49.87</v>
+        <v>48.29</v>
       </c>
       <c r="CB16" s="0" t="n">
         <v>0.0</v>
@@ -6896,7 +6896,7 @@
         <v>0.0</v>
       </c>
       <c r="CE16" s="0" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="CF16" s="0" t="n">
         <v>0.0</v>
@@ -6905,19 +6905,19 @@
         <v>0.0</v>
       </c>
       <c r="CH16" s="0" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="CI16" s="0" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="CJ16" s="0" t="n">
-        <v>38.46</v>
+        <v>34.62</v>
       </c>
       <c r="CK16" s="0" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="CL16" s="0" t="n">
-        <v>0.0</v>
+        <v>33.33</v>
       </c>
       <c r="CM16" s="0" t="n">
         <v>0.0</v>
@@ -6926,55 +6926,55 @@
         <v>0.0</v>
       </c>
       <c r="CO16" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="CP16" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ16" s="0" t="n">
-        <v>4.47</v>
+        <v>4.98</v>
       </c>
       <c r="CR16" s="0" t="n">
-        <v>42.62</v>
+        <v>49.61</v>
       </c>
       <c r="CS16" s="0" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="CT16" s="0" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="CU16" s="0" t="n">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="CV16" s="0" t="n">
-        <v>5.5</v>
+        <v>5.61</v>
       </c>
       <c r="CW16" s="0" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CX16" s="0" t="n">
-        <v>74.67</v>
+        <v>76.22</v>
       </c>
       <c r="CY16" s="0" t="n">
-        <v>18.55</v>
+        <v>36.86</v>
       </c>
       <c r="CZ16" s="0" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="DA16" s="0" t="n">
-        <v>-0.45</v>
+        <v>2.86</v>
       </c>
       <c r="DB16" s="0" t="n">
-        <v>-0.033</v>
+        <v>0.112</v>
       </c>
       <c r="DC16" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD16" s="0" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="DE16" s="0" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="DF16" s="0" t="inlineStr">
         <is>
@@ -7046,17 +7046,17 @@
     <row ht="12" customHeight="true" r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>T. Krantz</t>
+          <t>H. Keto</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>IFK Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>IFK Norrköping</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -7065,21 +7065,21 @@
         </is>
       </c>
       <c r="E17" s="0" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>2028-12-31</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="H17" s="0" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>1141</v>
+        <v>2344</v>
       </c>
       <c r="J17" s="0" t="n">
         <v>0</v>
@@ -7094,31 +7094,31 @@
         <v>0.0</v>
       </c>
       <c r="N17" s="0" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="O17" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="P17" s="0" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="Q17" s="0" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="R17" s="0" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S17" s="0" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="T17" s="0" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="U17" s="0" t="inlineStr">
         <is>
@@ -7126,178 +7126,178 @@
         </is>
       </c>
       <c r="V17" s="0" t="n">
-        <v>0.79</v>
+        <v>0.35</v>
       </c>
       <c r="W17" s="0" t="n">
-        <v>0.0</v>
+        <v>0.15</v>
       </c>
       <c r="X17" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="Y17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD17" s="0" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AE17" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AT17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF17" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BG17" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BH17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI17" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BJ17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK17" s="0" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="BL17" s="0" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BM17" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BN17" s="0" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="BO17" s="0" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="BP17" s="0" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="BQ17" s="0" t="n">
+        <v>67.15</v>
+      </c>
+      <c r="BR17" s="0" t="n">
         <v>0.08</v>
-      </c>
-      <c r="Z17" s="0" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AA17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD17" s="0" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="AE17" s="0" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AO17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AP17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AR17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AT17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AU17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AV17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AW17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AX17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AY17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AZ17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BA17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BB17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BC17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BD17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BE17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BF17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BG17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BH17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BI17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ17" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BK17" s="0" t="n">
-        <v>21.06</v>
-      </c>
-      <c r="BL17" s="0" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="BM17" s="0" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="BN17" s="0" t="n">
-        <v>35.81</v>
-      </c>
-      <c r="BO17" s="0" t="n">
-        <v>80.4</v>
-      </c>
-      <c r="BP17" s="0" t="n">
-        <v>17.98</v>
-      </c>
-      <c r="BQ17" s="0" t="n">
-        <v>66.23</v>
-      </c>
-      <c r="BR17" s="0" t="n">
-        <v>0.16</v>
       </c>
       <c r="BS17" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="BT17" s="0" t="n">
-        <v>15.85</v>
+        <v>9.75</v>
       </c>
       <c r="BU17" s="0" t="n">
-        <v>94.53</v>
+        <v>96.06</v>
       </c>
       <c r="BV17" s="0" t="n">
-        <v>23.82</v>
+        <v>15.28</v>
       </c>
       <c r="BW17" s="0" t="n">
-        <v>94.04</v>
+        <v>97.99</v>
       </c>
       <c r="BX17" s="0" t="n">
-        <v>11.99</v>
+        <v>8.83</v>
       </c>
       <c r="BY17" s="0" t="n">
-        <v>53.29</v>
+        <v>49.57</v>
       </c>
       <c r="BZ17" s="0" t="n">
-        <v>30.66</v>
+        <v>31.01</v>
       </c>
       <c r="CA17" s="0" t="n">
-        <v>48.15</v>
+        <v>50.93</v>
       </c>
       <c r="CB17" s="0" t="n">
         <v>0.0</v>
@@ -7306,7 +7306,7 @@
         <v>0.0</v>
       </c>
       <c r="CD17" s="0" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="CE17" s="0" t="n">
         <v>0.0</v>
@@ -7321,13 +7321,13 @@
         <v>0.0</v>
       </c>
       <c r="CI17" s="0" t="n">
-        <v>3.79</v>
+        <v>2.84</v>
       </c>
       <c r="CJ17" s="0" t="n">
-        <v>47.92</v>
+        <v>36.49</v>
       </c>
       <c r="CK17" s="0" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="CL17" s="0" t="n">
         <v>0.0</v>
@@ -7339,55 +7339,55 @@
         <v>0.0</v>
       </c>
       <c r="CO17" s="0" t="n">
-        <v>0.0</v>
+        <v>0.12</v>
       </c>
       <c r="CP17" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ17" s="0" t="n">
-        <v>9.78</v>
+        <v>6.72</v>
       </c>
       <c r="CR17" s="0" t="n">
-        <v>60.48</v>
+        <v>64.57</v>
       </c>
       <c r="CS17" s="0" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="CT17" s="0" t="n">
-        <v>0.63</v>
+        <v>1.5</v>
       </c>
       <c r="CU17" s="0" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="CV17" s="0" t="n">
-        <v>4.18</v>
+        <v>4.45</v>
       </c>
       <c r="CW17" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CX17" s="0" t="n">
-        <v>84.91</v>
+        <v>66.38</v>
       </c>
       <c r="CY17" s="0" t="n">
-        <v>13.56</v>
+        <v>34.14</v>
       </c>
       <c r="CZ17" s="0" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="DA17" s="0" t="n">
-        <v>5.56</v>
+        <v>-4.86</v>
       </c>
       <c r="DB17" s="0" t="n">
-        <v>0.439</v>
+        <v>-0.187</v>
       </c>
       <c r="DC17" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD17" s="0" t="n">
-        <v>2.6</v>
+        <v>1.19</v>
       </c>
       <c r="DE17" s="0" t="n">
-        <v>0.08</v>
+        <v>0.0</v>
       </c>
       <c r="DF17" s="0" t="inlineStr">
         <is>
@@ -7414,62 +7414,62 @@
         <v>0.0</v>
       </c>
       <c r="DL17" s="0" t="n">
-        <v>6675.72</v>
+        <v>5198.19</v>
       </c>
       <c r="DM17" s="0" t="n">
-        <v>252.13</v>
+        <v>109.17</v>
       </c>
       <c r="DN17" s="0" t="n">
-        <v>106.94</v>
+        <v>25.14</v>
       </c>
       <c r="DO17" s="0" t="n">
-        <v>14.84</v>
+        <v>3.03</v>
       </c>
       <c r="DP17" s="0" t="n">
-        <v>121.78</v>
+        <v>28.17</v>
       </c>
       <c r="DQ17" s="0" t="n">
-        <v>74.17</v>
+        <v>57.76</v>
       </c>
       <c r="DR17" s="0" t="n">
-        <v>32.34</v>
+        <v>32.59</v>
       </c>
       <c r="DS17" s="0" t="n">
-        <v>87.45</v>
+        <v>63.68</v>
       </c>
       <c r="DT17" s="0" t="n">
-        <v>8.16</v>
+        <v>5.4</v>
       </c>
       <c r="DU17" s="0" t="n">
-        <v>85.19</v>
+        <v>67.64</v>
       </c>
       <c r="DV17" s="0" t="n">
-        <v>8.16</v>
+        <v>5.04</v>
       </c>
       <c r="DW17" s="0" t="n">
-        <v>11.78</v>
+        <v>3.24</v>
       </c>
       <c r="DX17" s="0" t="n">
-        <v>0.91</v>
+        <v>0.36</v>
       </c>
       <c r="DY17" s="0" t="n">
-        <v>12.69</v>
+        <v>3.6</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>S. Banozic</t>
+          <t>O. Ekman</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Varbergs</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Varbergs</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="E18" s="0" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="H18" s="0" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>1360</v>
+        <v>1583</v>
       </c>
       <c r="J18" s="0" t="n">
         <v>0</v>
@@ -7501,16 +7501,16 @@
         <v>0.0</v>
       </c>
       <c r="L18" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="N18" s="0" t="n">
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>100.0</v>
+        <v>66.67</v>
       </c>
       <c r="P18" s="0" t="inlineStr">
         <is>
@@ -7524,14 +7524,14 @@
       </c>
       <c r="R18" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>right</t>
         </is>
       </c>
       <c r="S18" s="0" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="T18" s="0" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="U18" s="0" t="inlineStr">
         <is>
@@ -7539,13 +7539,13 @@
         </is>
       </c>
       <c r="V18" s="0" t="n">
-        <v>0.73</v>
+        <v>0.28</v>
       </c>
       <c r="W18" s="0" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="X18" s="0" t="n">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="Y18" s="0" t="n">
         <v>0.0</v>
@@ -7563,10 +7563,10 @@
         <v>0.0</v>
       </c>
       <c r="AD18" s="0" t="n">
-        <v>0.6</v>
+        <v>0.17</v>
       </c>
       <c r="AE18" s="0" t="n">
-        <v>0.64</v>
+        <v>0.23</v>
       </c>
       <c r="AF18" s="0" t="n">
         <v>0.0</v>
@@ -7584,7 +7584,7 @@
         <v>0.0</v>
       </c>
       <c r="AK18" s="0" t="n">
-        <v>0.07</v>
+        <v>0.0</v>
       </c>
       <c r="AL18" s="0" t="n">
         <v>0.0</v>
@@ -7617,7 +7617,7 @@
         <v>0.0</v>
       </c>
       <c r="AV18" s="0" t="n">
-        <v>0.0</v>
+        <v>0.06</v>
       </c>
       <c r="AW18" s="0" t="n">
         <v>0.0</v>
@@ -7647,7 +7647,7 @@
         <v>0.0</v>
       </c>
       <c r="BF18" s="0" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="BG18" s="0" t="n">
         <v>100.0</v>
@@ -7659,28 +7659,28 @@
         <v>0.0</v>
       </c>
       <c r="BJ18" s="0" t="n">
-        <v>0.07</v>
+        <v>0.0</v>
       </c>
       <c r="BK18" s="0" t="n">
-        <v>15.22</v>
+        <v>13.19</v>
       </c>
       <c r="BL18" s="0" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="BM18" s="0" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="BN18" s="0" t="n">
-        <v>27.46</v>
+        <v>22.74</v>
       </c>
       <c r="BO18" s="0" t="n">
-        <v>83.86</v>
+        <v>76.25</v>
       </c>
       <c r="BP18" s="0" t="n">
-        <v>14.23</v>
+        <v>14.1</v>
       </c>
       <c r="BQ18" s="0" t="n">
-        <v>73.02</v>
+        <v>66.13</v>
       </c>
       <c r="BR18" s="0" t="n">
         <v>0.0</v>
@@ -7689,28 +7689,28 @@
         <v>0.0</v>
       </c>
       <c r="BT18" s="0" t="n">
-        <v>12.44</v>
+        <v>7.79</v>
       </c>
       <c r="BU18" s="0" t="n">
-        <v>95.74</v>
+        <v>94.89</v>
       </c>
       <c r="BV18" s="0" t="n">
-        <v>17.4</v>
+        <v>11.88</v>
       </c>
       <c r="BW18" s="0" t="n">
-        <v>98.48</v>
+        <v>96.65</v>
       </c>
       <c r="BX18" s="0" t="n">
-        <v>9.93</v>
+        <v>10.86</v>
       </c>
       <c r="BY18" s="0" t="n">
-        <v>59.33</v>
+        <v>53.93</v>
       </c>
       <c r="BZ18" s="0" t="n">
-        <v>34.23</v>
+        <v>37.71</v>
       </c>
       <c r="CA18" s="0" t="n">
-        <v>50.43</v>
+        <v>52.03</v>
       </c>
       <c r="CB18" s="0" t="n">
         <v>0.0</v>
@@ -7719,85 +7719,85 @@
         <v>0.0</v>
       </c>
       <c r="CD18" s="0" t="n">
-        <v>0.0</v>
+        <v>0.06</v>
       </c>
       <c r="CE18" s="0" t="n">
-        <v>0.0</v>
+        <v>0.06</v>
       </c>
       <c r="CF18" s="0" t="n">
-        <v>0.07</v>
+        <v>0.0</v>
       </c>
       <c r="CG18" s="0" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="CH18" s="0" t="n">
-        <v>0.0</v>
+        <v>0.06</v>
       </c>
       <c r="CI18" s="0" t="n">
-        <v>2.91</v>
+        <v>3.47</v>
       </c>
       <c r="CJ18" s="0" t="n">
-        <v>61.36</v>
+        <v>42.62</v>
       </c>
       <c r="CK18" s="0" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="CL18" s="0" t="n">
-        <v>33.33</v>
+        <v>18.18</v>
       </c>
       <c r="CM18" s="0" t="n">
-        <v>0.13</v>
+        <v>0.0</v>
       </c>
       <c r="CN18" s="0" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="CO18" s="0" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="CP18" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ18" s="0" t="n">
-        <v>8.14</v>
+        <v>8.76</v>
       </c>
       <c r="CR18" s="0" t="n">
-        <v>66.67</v>
+        <v>67.53</v>
       </c>
       <c r="CS18" s="0" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="CT18" s="0" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="CU18" s="0" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="CV18" s="0" t="n">
-        <v>3.84</v>
+        <v>3.47</v>
       </c>
       <c r="CW18" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CX18" s="0" t="n">
-        <v>65.52</v>
+        <v>63.93</v>
       </c>
       <c r="CY18" s="0" t="n">
-        <v>18.98</v>
+        <v>22.1</v>
       </c>
       <c r="CZ18" s="0" t="n">
         <v>1.26</v>
       </c>
       <c r="DA18" s="0" t="n">
-        <v>-1.02</v>
+        <v>0.1</v>
       </c>
       <c r="DB18" s="0" t="n">
-        <v>-0.068</v>
+        <v>0.006</v>
       </c>
       <c r="DC18" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD18" s="0" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DE18" s="0" t="n">
         <v>0.0</v>
@@ -7827,46 +7827,46 @@
         <v>0.0</v>
       </c>
       <c r="DL18" s="0" t="n">
-        <v>6110.42</v>
+        <v>5053.41</v>
       </c>
       <c r="DM18" s="0" t="n">
-        <v>183.89</v>
+        <v>89.76</v>
       </c>
       <c r="DN18" s="0" t="n">
-        <v>48.98</v>
+        <v>16.19</v>
       </c>
       <c r="DO18" s="0" t="n">
-        <v>21.62</v>
+        <v>5.62</v>
       </c>
       <c r="DP18" s="0" t="n">
-        <v>70.6</v>
+        <v>21.81</v>
       </c>
       <c r="DQ18" s="0" t="n">
-        <v>67.89</v>
+        <v>56.15</v>
       </c>
       <c r="DR18" s="0" t="n">
-        <v>34.16</v>
+        <v>29.35</v>
       </c>
       <c r="DS18" s="0" t="n">
-        <v>69.69</v>
+        <v>52.37</v>
       </c>
       <c r="DT18" s="0" t="n">
-        <v>6.35</v>
+        <v>4.49</v>
       </c>
       <c r="DU18" s="0" t="n">
-        <v>77.89</v>
+        <v>50.57</v>
       </c>
       <c r="DV18" s="0" t="n">
-        <v>7.14</v>
+        <v>3.59</v>
       </c>
       <c r="DW18" s="0" t="n">
-        <v>4.36</v>
+        <v>2.09</v>
       </c>
       <c r="DX18" s="0" t="n">
-        <v>1.85</v>
+        <v>0.3</v>
       </c>
       <c r="DY18" s="0" t="n">
-        <v>6.22</v>
+        <v>2.39</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="19">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H19" s="0" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>1086</v>
+        <v>1275</v>
       </c>
       <c r="J19" s="0" t="n">
         <v>0</v>
@@ -7920,7 +7920,7 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="0" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="O19" s="0" t="n">
         <v>50.0</v>
@@ -7952,16 +7952,16 @@
         </is>
       </c>
       <c r="V19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="W19" s="0" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="X19" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="Y19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="Z19" s="0" t="n">
         <v>66.67</v>
@@ -7976,19 +7976,19 @@
         <v>0.0</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
       <c r="AG19" s="0" t="n">
         <v>2</v>
       </c>
       <c r="AH19" s="0" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AI19" s="0" t="n">
         <v>0</v>
@@ -8060,7 +8060,7 @@
         <v>0.0</v>
       </c>
       <c r="BF19" s="0" t="n">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
       <c r="BG19" s="0" t="n">
         <v>100.0</v>
@@ -8075,55 +8075,55 @@
         <v>0.0</v>
       </c>
       <c r="BK19" s="0" t="n">
-        <v>11.1</v>
+        <v>11.44</v>
       </c>
       <c r="BL19" s="0" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="BM19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BN19" s="0" t="n">
-        <v>19.48</v>
+        <v>19.69</v>
       </c>
       <c r="BO19" s="0" t="n">
-        <v>70.64</v>
+        <v>70.25</v>
       </c>
       <c r="BP19" s="0" t="n">
-        <v>11.19</v>
+        <v>11.15</v>
       </c>
       <c r="BQ19" s="0" t="n">
-        <v>54.81</v>
+        <v>53.16</v>
       </c>
       <c r="BR19" s="0" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BS19" s="0" t="n">
         <v>50.0</v>
       </c>
       <c r="BT19" s="0" t="n">
-        <v>6.88</v>
+        <v>6.92</v>
       </c>
       <c r="BU19" s="0" t="n">
-        <v>92.77</v>
+        <v>93.88</v>
       </c>
       <c r="BV19" s="0" t="n">
-        <v>10.36</v>
+        <v>10.52</v>
       </c>
       <c r="BW19" s="0" t="n">
-        <v>96.8</v>
+        <v>96.64</v>
       </c>
       <c r="BX19" s="0" t="n">
-        <v>9.03</v>
+        <v>9.11</v>
       </c>
       <c r="BY19" s="0" t="n">
-        <v>41.28</v>
+        <v>40.31</v>
       </c>
       <c r="BZ19" s="0" t="n">
-        <v>35.05</v>
+        <v>35.2</v>
       </c>
       <c r="CA19" s="0" t="n">
-        <v>51.63</v>
+        <v>51.44</v>
       </c>
       <c r="CB19" s="0" t="n">
         <v>0.0</v>
@@ -8147,13 +8147,13 @@
         <v>0.0</v>
       </c>
       <c r="CI19" s="0" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="CJ19" s="0" t="n">
-        <v>33.33</v>
+        <v>29.03</v>
       </c>
       <c r="CK19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="CL19" s="0" t="n">
         <v>0.0</v>
@@ -8171,49 +8171,49 @@
         <v>0.0</v>
       </c>
       <c r="CQ19" s="0" t="n">
-        <v>6.8</v>
+        <v>6.78</v>
       </c>
       <c r="CR19" s="0" t="n">
-        <v>52.44</v>
+        <v>50.0</v>
       </c>
       <c r="CS19" s="0" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CT19" s="0" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="CU19" s="0" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="CV19" s="0" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="CW19" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CX19" s="0" t="n">
-        <v>61.54</v>
+        <v>62.22</v>
       </c>
       <c r="CY19" s="0" t="n">
-        <v>13.14</v>
+        <v>14.78</v>
       </c>
       <c r="CZ19" s="0" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="DA19" s="0" t="n">
-        <v>-1.86</v>
+        <v>-2.22</v>
       </c>
       <c r="DB19" s="0" t="n">
-        <v>-0.154</v>
+        <v>-0.157</v>
       </c>
       <c r="DC19" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD19" s="0" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="DE19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="DF19" s="0" t="inlineStr">
         <is>
@@ -8280,6 +8280,2211 @@
       </c>
       <c r="DY19" s="0" t="n">
         <v>1.82</v>
+      </c>
+    </row>
+    <row ht="12" customHeight="true" r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>R. Forsell</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Östersunds FK</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Östersunds FK</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>2028-12-31</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>764</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="0" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O20" s="0" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="P20" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="Q20" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="R20" s="0" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="S20" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="T20" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="U20" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="V20" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W20" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD20" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AE20" s="0" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AF20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AT20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF20" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BG20" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BH20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BJ20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK20" s="0" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="BL20" s="0" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BM20" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BN20" s="0" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="BO20" s="0" t="n">
+        <v>79.31</v>
+      </c>
+      <c r="BP20" s="0" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="BQ20" s="0" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="BR20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT20" s="0" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="BU20" s="0" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="BV20" s="0" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="BW20" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BX20" s="0" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="BY20" s="0" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="BZ20" s="0" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="CA20" s="0" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="CB20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI20" s="0" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CJ20" s="0" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="CK20" s="0" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="CL20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CM20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CN20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CO20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CP20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CQ20" s="0" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="CR20" s="0" t="n">
+        <v>73.08</v>
+      </c>
+      <c r="CS20" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT20" s="0" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CU20" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV20" s="0" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CW20" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="CX20" s="0" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="CY20" s="0" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="CZ20" s="0" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DA20" s="0" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DB20" s="0" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="DC20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD20" s="0" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DE20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DF20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DG20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DH20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DI20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DJ20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK20" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DL20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DM20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DN20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DO20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DP20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DQ20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DR20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DS20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DT20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DU20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DV20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DW20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DX20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DY20" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row ht="12" customHeight="true" r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>H. Sveijer</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>776</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="0" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O21" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="P21" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="Q21" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="R21" s="0" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="S21" s="0" t="n">
+        <v>187</v>
+      </c>
+      <c r="T21" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="U21" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="V21" s="0" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="W21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y21" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z21" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="AA21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD21" s="0" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AE21" s="0" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AF21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AT21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BG21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BH21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BJ21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK21" s="0" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="BL21" s="0" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BM21" s="0" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BN21" s="0" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="BO21" s="0" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="BP21" s="0" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="BQ21" s="0" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="BR21" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BS21" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BT21" s="0" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="BU21" s="0" t="n">
+        <v>98.72</v>
+      </c>
+      <c r="BV21" s="0" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="BW21" s="0" t="n">
+        <v>98.27</v>
+      </c>
+      <c r="BX21" s="0" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="BY21" s="0" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="BZ21" s="0" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="CA21" s="0" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="CB21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI21" s="0" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CJ21" s="0" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="CK21" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="CL21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CM21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CN21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CO21" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="CP21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CQ21" s="0" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="CR21" s="0" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="CS21" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT21" s="0" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CU21" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="CV21" s="0" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="CW21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX21" s="0" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="CY21" s="0" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="CZ21" s="0" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DA21" s="0" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="DB21" s="0" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="DC21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD21" s="0" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DE21" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DG21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DH21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DI21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DJ21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DL21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DM21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DN21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DO21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DP21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DQ21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DR21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DS21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DT21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DU21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DV21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DW21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DX21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DY21" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row ht="12" customHeight="true" r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>A. Dzevlan</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>United Nordic</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>United Nordic</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>951</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O22" s="0" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="P22" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="Q22" s="0" t="inlineStr">
+        <is>
+          <t>Sweden, Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="R22" s="0" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="S22" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="T22" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="U22" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="V22" s="0" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" s="0" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD22" s="0" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE22" s="0" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF22" s="0" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG22" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH22" s="0" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ22" s="0" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AT22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF22" s="0" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BG22" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BH22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BJ22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK22" s="0" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="BL22" s="0" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BM22" s="0" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BN22" s="0" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="BO22" s="0" t="n">
+        <v>84.18</v>
+      </c>
+      <c r="BP22" s="0" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="BQ22" s="0" t="n">
+        <v>74.58</v>
+      </c>
+      <c r="BR22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT22" s="0" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="BU22" s="0" t="n">
+        <v>96.95</v>
+      </c>
+      <c r="BV22" s="0" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="BW22" s="0" t="n">
+        <v>97.76</v>
+      </c>
+      <c r="BX22" s="0" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="BY22" s="0" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="BZ22" s="0" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="CA22" s="0" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="CB22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE22" s="0" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="CF22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI22" s="0" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="CJ22" s="0" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="CK22" s="0" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="CL22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CM22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CN22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CO22" s="0" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="CP22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CQ22" s="0" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="CR22" s="0" t="n">
+        <v>67.71</v>
+      </c>
+      <c r="CS22" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT22" s="0" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CU22" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="CV22" s="0" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="CW22" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX22" s="0" t="n">
+        <v>68.09</v>
+      </c>
+      <c r="CY22" s="0" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="CZ22" s="0" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DA22" s="0" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="DB22" s="0" t="n">
+        <v>-0.117</v>
+      </c>
+      <c r="DC22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD22" s="0" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="DE22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DF22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DG22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DH22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DI22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DJ22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK22" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DL22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DM22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DN22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DO22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DP22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DQ22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DR22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DS22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DT22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DU22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DV22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DW22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DX22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DY22" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row ht="12" customHeight="true" r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>E. Rådahl</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>2028-12-31</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>585</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="0" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O23" s="0" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="P23" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="Q23" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="R23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="V23" s="0" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="W23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y23" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Z23" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="AA23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD23" s="0" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AE23" s="0" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AF23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AT23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF23" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BG23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BH23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BJ23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK23" s="0" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="BL23" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BM23" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BN23" s="0" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="BO23" s="0" t="n">
+        <v>81.59</v>
+      </c>
+      <c r="BP23" s="0" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="BQ23" s="0" t="n">
+        <v>68.47</v>
+      </c>
+      <c r="BR23" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BS23" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BT23" s="0" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="BU23" s="0" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="BV23" s="0" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="BW23" s="0" t="n">
+        <v>96.77</v>
+      </c>
+      <c r="BX23" s="0" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="BY23" s="0" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="BZ23" s="0" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="CA23" s="0" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="CB23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI23" s="0" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CJ23" s="0" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="CK23" s="0" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="CL23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CM23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CN23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CO23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CP23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CQ23" s="0" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="CR23" s="0" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="CS23" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT23" s="0" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CU23" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="CV23" s="0" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="CW23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX23" s="0" t="n">
+        <v>72.41</v>
+      </c>
+      <c r="CY23" s="0" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="CZ23" s="0" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DA23" s="0" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DB23" s="0" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="DC23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD23" s="0" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DE23" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DF23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DG23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DH23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DI23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DJ23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DL23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DM23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DN23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DO23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DP23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DQ23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DR23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DS23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DT23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DU23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DV23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DW23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DX23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DY23" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row ht="12" customHeight="true" r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>K. Strindholm</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>Varbergs</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>Varbergs</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>75000</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>2027-12-31</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>865</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O24" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="P24" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="Q24" s="0" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="R24" s="0" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="S24" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="T24" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="U24" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="V24" s="0" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="W24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD24" s="0" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AE24" s="0" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AF24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO24" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AP24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AT24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF24" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BG24" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BH24" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BI24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BJ24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK24" s="0" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="BL24" s="0" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BM24" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BN24" s="0" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="BO24" s="0" t="n">
+        <v>77.93</v>
+      </c>
+      <c r="BP24" s="0" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="BQ24" s="0" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="BR24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT24" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU24" s="0" t="n">
+        <v>95.89</v>
+      </c>
+      <c r="BV24" s="0" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="BW24" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BX24" s="0" t="n">
+        <v>8.12</v>
+      </c>
+      <c r="BY24" s="0" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="BZ24" s="0" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="CA24" s="0" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="CB24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI24" s="0" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CJ24" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="CK24" s="0" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CL24" s="0" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="CM24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CN24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CO24" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CP24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CQ24" s="0" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="CR24" s="0" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="CS24" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT24" s="0" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CU24" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="CV24" s="0" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="CW24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX24" s="0" t="n">
+        <v>75.56</v>
+      </c>
+      <c r="CY24" s="0" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="CZ24" s="0" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DA24" s="0" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="DB24" s="0" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="DC24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD24" s="0" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DE24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DF24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DG24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DH24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DI24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DJ24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DL24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DM24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DN24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DO24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DP24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DQ24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DR24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DS24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DT24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DU24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DV24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DW24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DX24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DY24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
   </sheetData>
